--- a/research/traditional_assets/database/data/malaysia/malaysia_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_rubber_tires.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="klse_esafe" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,106 +590,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.106</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.01468659847888802</v>
+        <v>-0.1106651698007297</v>
       </c>
       <c r="H2">
-        <v>-0.01468659847888802</v>
+        <v>-0.1106651698007297</v>
       </c>
       <c r="I2">
-        <v>-0.03514293207448204</v>
+        <v>-0.1250070165590794</v>
       </c>
       <c r="J2">
-        <v>-0.03514293207448204</v>
+        <v>-0.09375526241930957</v>
       </c>
       <c r="K2">
-        <v>-2.811</v>
+        <v>-2.326</v>
       </c>
       <c r="L2">
-        <v>-0.07372147915027538</v>
+        <v>-0.06528206567499296</v>
       </c>
       <c r="M2">
-        <v>0.414</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.01792207792207792</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.1472785485592316</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.414</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.01792207792207792</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.1472785485592316</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>6.81</v>
+        <v>5.318000000000001</v>
       </c>
       <c r="V2">
-        <v>0.2948051948051948</v>
+        <v>0.2262978723404256</v>
+      </c>
+      <c r="W2">
+        <v>-0.08681705110809587</v>
       </c>
       <c r="X2">
-        <v>0.1487067518951054</v>
+        <v>0.1127720056956368</v>
+      </c>
+      <c r="Y2">
+        <v>-0.1995890568037327</v>
       </c>
       <c r="Z2">
-        <v>1.952380952380952</v>
+        <v>1.056642941874259</v>
+      </c>
+      <c r="AA2">
+        <v>-0.1662977801412834</v>
       </c>
       <c r="AB2">
-        <v>0.1124021945009818</v>
+        <v>0.09230006258143153</v>
+      </c>
+      <c r="AC2">
+        <v>-0.2585978427227149</v>
       </c>
       <c r="AD2">
-        <v>13.93</v>
+        <v>10.88</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>13.93</v>
+        <v>10.88</v>
       </c>
       <c r="AG2">
-        <v>7.12</v>
+        <v>5.561999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.3761814744801512</v>
+        <v>0.3164630599185573</v>
       </c>
       <c r="AI2">
-        <v>0.338682227084853</v>
+        <v>0.3173862310385064</v>
       </c>
       <c r="AJ2">
-        <v>0.2356055592322965</v>
+        <v>0.191383937788177</v>
       </c>
       <c r="AK2">
-        <v>0.2074592074592075</v>
+        <v>0.1920447482908639</v>
       </c>
       <c r="AL2">
-        <v>0.627</v>
+        <v>0.758</v>
       </c>
       <c r="AM2">
-        <v>0.62</v>
+        <v>0.707</v>
       </c>
       <c r="AN2">
-        <v>19.73087818696884</v>
+        <v>-3.700680272108843</v>
       </c>
       <c r="AO2">
-        <v>-2.137161084529505</v>
+        <v>-5.87598944591029</v>
       </c>
       <c r="AP2">
-        <v>10.08498583569405</v>
+        <v>-1.891836734693877</v>
       </c>
       <c r="AQ2">
-        <v>-2.161290322580645</v>
+        <v>-6.2998585572843</v>
       </c>
     </row>
     <row r="3">
@@ -707,118 +718,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.106</v>
+        <v>0.0278</v>
       </c>
       <c r="G3">
-        <v>0.07340067340067341</v>
+        <v>0.01359259259259259</v>
       </c>
       <c r="H3">
-        <v>0.07340067340067341</v>
+        <v>0.01359259259259259</v>
       </c>
       <c r="I3">
-        <v>-0.008417508417508417</v>
+        <v>0.02022222222222222</v>
       </c>
       <c r="J3">
-        <v>-0.008417508417508417</v>
+        <v>0.01011111111111111</v>
       </c>
       <c r="K3">
-        <v>-0.631</v>
+        <v>-0.046</v>
       </c>
       <c r="L3">
-        <v>-0.02124579124579124</v>
+        <v>-0.001703703703703704</v>
       </c>
       <c r="M3">
-        <v>0.414</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03763636363636363</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.6561014263074485</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.414</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03763636363636363</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.6561014263074485</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>5.1</v>
+        <v>4.78</v>
       </c>
       <c r="V3">
-        <v>0.4636363636363636</v>
+        <v>0.4230088495575221</v>
       </c>
       <c r="W3">
-        <v>-0.03993670886075949</v>
+        <v>-0.003484848484848485</v>
       </c>
       <c r="X3">
-        <v>0.1711840056835415</v>
+        <v>0.1273295524111663</v>
       </c>
       <c r="Y3">
-        <v>-0.211120714544301</v>
+        <v>-0.1308144008960148</v>
       </c>
       <c r="Z3">
-        <v>1.52073732718894</v>
+        <v>1.398963730569948</v>
       </c>
       <c r="AA3">
-        <v>-0.01280081925243215</v>
+        <v>0.01414507772020726</v>
       </c>
       <c r="AB3">
-        <v>0.1115333804506845</v>
+        <v>0.09162938579178047</v>
       </c>
       <c r="AC3">
-        <v>-0.1243341997031166</v>
+        <v>-0.07748430807157321</v>
       </c>
       <c r="AD3">
-        <v>11.2</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11.2</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AG3">
-        <v>6.1</v>
+        <v>4.589999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.5045045045045045</v>
+        <v>0.4533139816158683</v>
       </c>
       <c r="AI3">
-        <v>0.459016393442623</v>
+        <v>0.4170004450378282</v>
       </c>
       <c r="AJ3">
-        <v>0.3567251461988303</v>
+        <v>0.2888609188168659</v>
       </c>
       <c r="AK3">
-        <v>0.3160621761658031</v>
+        <v>0.2594686263425664</v>
       </c>
       <c r="AL3">
-        <v>0.384</v>
+        <v>0.549</v>
       </c>
       <c r="AM3">
-        <v>0.384</v>
+        <v>0.4980000000000001</v>
       </c>
       <c r="AN3">
-        <v>15.86402266288952</v>
+        <v>6.374149659863945</v>
       </c>
       <c r="AO3">
-        <v>-0.6510416666666666</v>
+        <v>0.9945355191256831</v>
       </c>
       <c r="AP3">
-        <v>8.640226628895183</v>
+        <v>3.122448979591836</v>
       </c>
       <c r="AQ3">
-        <v>-0.6510416666666666</v>
+        <v>1.096385542168675</v>
       </c>
     </row>
     <row r="4">
@@ -837,23 +845,26 @@
           <t>Rubber&amp; Tires</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.197</v>
+      </c>
       <c r="G4">
-        <v>-0.3250296559905101</v>
+        <v>-0.4994206257242177</v>
       </c>
       <c r="H4">
-        <v>-0.3250296559905101</v>
+        <v>-0.4994206257242177</v>
       </c>
       <c r="I4">
-        <v>-0.129300118623962</v>
+        <v>-0.5793742757821552</v>
       </c>
       <c r="J4">
-        <v>-0.129300118623962</v>
+        <v>-0.5793742757821552</v>
       </c>
       <c r="K4">
-        <v>-2.18</v>
+        <v>-2.28</v>
       </c>
       <c r="L4">
-        <v>-0.2586002372479241</v>
+        <v>-0.2641946697566628</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,52 +888,8845 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.71</v>
+        <v>0.538</v>
       </c>
       <c r="V4">
-        <v>0.1413223140495868</v>
+        <v>0.04409836065573771</v>
+      </c>
+      <c r="W4">
+        <v>-0.1701492537313433</v>
       </c>
       <c r="X4">
-        <v>0.1262294981066693</v>
+        <v>0.09821445898010731</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2683637127114505</v>
+      </c>
+      <c r="Z4">
+        <v>0.598474341192788</v>
+      </c>
+      <c r="AA4">
+        <v>-0.346740638002774</v>
       </c>
       <c r="AB4">
-        <v>0.1132710085512791</v>
+        <v>0.09297073937108259</v>
+      </c>
+      <c r="AC4">
+        <v>-0.4397113773738566</v>
       </c>
       <c r="AD4">
-        <v>2.73</v>
+        <v>1.51</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.73</v>
+        <v>1.51</v>
       </c>
       <c r="AG4">
-        <v>1.02</v>
+        <v>0.972</v>
       </c>
       <c r="AH4">
-        <v>0.1840863115306811</v>
+        <v>0.1101385849744712</v>
       </c>
       <c r="AI4">
-        <v>0.1631799163179916</v>
+        <v>0.1278577476714648</v>
       </c>
       <c r="AJ4">
-        <v>0.07774390243902439</v>
+        <v>0.07379289401761312</v>
       </c>
       <c r="AK4">
-        <v>0.06790945406125166</v>
+        <v>0.08623136976579134</v>
       </c>
       <c r="AL4">
-        <v>0.243</v>
+        <v>0.209</v>
       </c>
       <c r="AM4">
-        <v>0.236</v>
+        <v>0.209</v>
+      </c>
+      <c r="AN4">
+        <v>-0.3424036281179138</v>
       </c>
       <c r="AO4">
-        <v>-4.485596707818931</v>
+        <v>-23.92344497607656</v>
+      </c>
+      <c r="AP4">
+        <v>-0.2204081632653061</v>
       </c>
       <c r="AQ4">
-        <v>-4.618644067796611</v>
+        <v>-23.92344497607656</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Eversafe Rubber Berhad (KLSE:ESAFE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KLSE:ESAFE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Rubber&amp; Tires</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.9945355191256831</v>
+      </c>
+      <c r="F2">
+        <v>4.53258853933503</v>
+      </c>
+      <c r="G2">
+        <v>6.37414965986394</v>
+      </c>
+      <c r="H2">
+        <v>4.49959183673469</v>
+      </c>
+      <c r="I2">
+        <v>0.453313981615868</v>
+      </c>
+      <c r="J2">
+        <v>0.32</v>
+      </c>
+      <c r="K2">
+        <v>11.3</v>
+      </c>
+      <c r="L2">
+        <v>14.9218386486327</v>
+      </c>
+      <c r="M2">
+        <v>15.89</v>
+      </c>
+      <c r="N2">
+        <v>16.7562386486327</v>
+      </c>
+      <c r="O2">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="P2">
+        <v>6.6144</v>
+      </c>
+      <c r="Q2">
+        <v>0.0916293857917805</v>
+      </c>
+      <c r="R2">
+        <v>0.08889829221427881</v>
+      </c>
+      <c r="S2">
+        <v>0.048575823059757</v>
+      </c>
+      <c r="T2">
+        <v>0.038684</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.127329552411166</v>
+      </c>
+      <c r="X2">
+        <v>0.112528547373939</v>
+      </c>
+      <c r="Y2">
+        <v>1.39344184703618</v>
+      </c>
+      <c r="Z2">
+        <v>1.16047625266293</v>
+      </c>
+      <c r="AA2">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.06391555665757501</v>
+      </c>
+      <c r="AC2">
+        <v>0.9945355191256831</v>
+      </c>
+      <c r="AD2">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0.549</v>
+      </c>
+      <c r="AF2">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="AG2">
+        <v>1.47</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>11.3</v>
+      </c>
+      <c r="AK2">
+        <v>0.06353300828410362</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.24</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>1.934</v>
+      </c>
+      <c r="AR2">
+        <v>0.549</v>
+      </c>
+      <c r="AS2">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="AT2">
+        <v>4.78</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09310612241581326</v>
+      </c>
+      <c r="C2">
+        <v>20.23790608660639</v>
+      </c>
+      <c r="D2">
+        <v>15.45790608660639</v>
+      </c>
+      <c r="E2">
+        <v>-9.369999999999999</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>4.78</v>
+      </c>
+      <c r="H2">
+        <v>11.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2.45</v>
+      </c>
+      <c r="K2">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L2">
+        <v>1.526</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.526</v>
+      </c>
+      <c r="O2">
+        <v>0.3662400000000001</v>
+      </c>
+      <c r="P2">
+        <v>1.15976</v>
+      </c>
+      <c r="Q2">
+        <v>2.08376</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09310612241581326</v>
+      </c>
+      <c r="T2">
+        <v>0.8547702034345668</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.033972</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09292750772201532</v>
+      </c>
+      <c r="C3">
+        <v>20.0822154398653</v>
+      </c>
+      <c r="D3">
+        <v>15.5089154398653</v>
+      </c>
+      <c r="E3">
+        <v>-9.1633</v>
+      </c>
+      <c r="F3">
+        <v>0.2067</v>
+      </c>
+      <c r="G3">
+        <v>4.78</v>
+      </c>
+      <c r="H3">
+        <v>11.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2.45</v>
+      </c>
+      <c r="K3">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L3">
+        <v>1.526</v>
+      </c>
+      <c r="M3">
+        <v>0.009239490000000001</v>
+      </c>
+      <c r="N3">
+        <v>1.51676051</v>
+      </c>
+      <c r="O3">
+        <v>0.3640225224</v>
+      </c>
+      <c r="P3">
+        <v>1.1527379876</v>
+      </c>
+      <c r="Q3">
+        <v>2.076737987600001</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09352301790102557</v>
+      </c>
+      <c r="T3">
+        <v>0.8613320757033575</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.033972</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>165.1606311603779</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09274889302821736</v>
+      </c>
+      <c r="C4">
+        <v>19.92686255797913</v>
+      </c>
+      <c r="D4">
+        <v>15.56026255797913</v>
+      </c>
+      <c r="E4">
+        <v>-8.9566</v>
+      </c>
+      <c r="F4">
+        <v>0.4134</v>
+      </c>
+      <c r="G4">
+        <v>4.78</v>
+      </c>
+      <c r="H4">
+        <v>11.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2.45</v>
+      </c>
+      <c r="K4">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L4">
+        <v>1.526</v>
+      </c>
+      <c r="M4">
+        <v>0.01847898</v>
+      </c>
+      <c r="N4">
+        <v>1.50752102</v>
+      </c>
+      <c r="O4">
+        <v>0.3618050448</v>
+      </c>
+      <c r="P4">
+        <v>1.1457159752</v>
+      </c>
+      <c r="Q4">
+        <v>2.0697159752</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09394842145736465</v>
+      </c>
+      <c r="T4">
+        <v>0.8680278637327355</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.033972</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>82.58031558018895</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09257027833441941</v>
+      </c>
+      <c r="C5">
+        <v>19.77185080692074</v>
+      </c>
+      <c r="D5">
+        <v>15.61195080692073</v>
+      </c>
+      <c r="E5">
+        <v>-8.749899999999998</v>
+      </c>
+      <c r="F5">
+        <v>0.6201</v>
+      </c>
+      <c r="G5">
+        <v>4.78</v>
+      </c>
+      <c r="H5">
+        <v>11.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2.45</v>
+      </c>
+      <c r="K5">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L5">
+        <v>1.526</v>
+      </c>
+      <c r="M5">
+        <v>0.02771847</v>
+      </c>
+      <c r="N5">
+        <v>1.49828153</v>
+      </c>
+      <c r="O5">
+        <v>0.3595875672000001</v>
+      </c>
+      <c r="P5">
+        <v>1.1386939628</v>
+      </c>
+      <c r="Q5">
+        <v>2.0626939628</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09438259622105094</v>
+      </c>
+      <c r="T5">
+        <v>0.8748617092472556</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.033972</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>55.05354372012597</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09239166364062147</v>
+      </c>
+      <c r="C6">
+        <v>19.61718359753657</v>
+      </c>
+      <c r="D6">
+        <v>15.66398359753657</v>
+      </c>
+      <c r="E6">
+        <v>-8.543199999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.8268000000000001</v>
+      </c>
+      <c r="G6">
+        <v>4.78</v>
+      </c>
+      <c r="H6">
+        <v>11.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2.45</v>
+      </c>
+      <c r="K6">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L6">
+        <v>1.526</v>
+      </c>
+      <c r="M6">
+        <v>0.03695796</v>
+      </c>
+      <c r="N6">
+        <v>1.48904204</v>
+      </c>
+      <c r="O6">
+        <v>0.3573700896000001</v>
+      </c>
+      <c r="P6">
+        <v>1.1316719504</v>
+      </c>
+      <c r="Q6">
+        <v>2.0556719504</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09482581629231403</v>
+      </c>
+      <c r="T6">
+        <v>0.8818379265433282</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.033972</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>41.29015779009448</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.0922130489468235</v>
+      </c>
+      <c r="C7">
+        <v>19.46286438629693</v>
+      </c>
+      <c r="D7">
+        <v>15.71636438629693</v>
+      </c>
+      <c r="E7">
+        <v>-8.336499999999999</v>
+      </c>
+      <c r="F7">
+        <v>1.0335</v>
+      </c>
+      <c r="G7">
+        <v>4.78</v>
+      </c>
+      <c r="H7">
+        <v>11.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2.45</v>
+      </c>
+      <c r="K7">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L7">
+        <v>1.526</v>
+      </c>
+      <c r="M7">
+        <v>0.04619745000000001</v>
+      </c>
+      <c r="N7">
+        <v>1.47980255</v>
+      </c>
+      <c r="O7">
+        <v>0.355152612</v>
+      </c>
+      <c r="P7">
+        <v>1.124649938</v>
+      </c>
+      <c r="Q7">
+        <v>2.048649938</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09527836731244579</v>
+      </c>
+      <c r="T7">
+        <v>0.8889610115719495</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.033972</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>33.03212623207558</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09203443425302554</v>
+      </c>
+      <c r="C8">
+        <v>19.30889667606135</v>
+      </c>
+      <c r="D8">
+        <v>15.76909667606135</v>
+      </c>
+      <c r="E8">
+        <v>-8.129799999999999</v>
+      </c>
+      <c r="F8">
+        <v>1.2402</v>
+      </c>
+      <c r="G8">
+        <v>4.78</v>
+      </c>
+      <c r="H8">
+        <v>11.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2.45</v>
+      </c>
+      <c r="K8">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L8">
+        <v>1.526</v>
+      </c>
+      <c r="M8">
+        <v>0.05543694</v>
+      </c>
+      <c r="N8">
+        <v>1.47056306</v>
+      </c>
+      <c r="O8">
+        <v>0.3529351344</v>
+      </c>
+      <c r="P8">
+        <v>1.1176279256</v>
+      </c>
+      <c r="Q8">
+        <v>2.0416279256</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09574054707768676</v>
+      </c>
+      <c r="T8">
+        <v>0.8962356516011798</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.033972</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>27.52677186006298</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09185581955922759</v>
+      </c>
+      <c r="C9">
+        <v>19.15528401685949</v>
+      </c>
+      <c r="D9">
+        <v>15.82218401685949</v>
+      </c>
+      <c r="E9">
+        <v>-7.923099999999999</v>
+      </c>
+      <c r="F9">
+        <v>1.4469</v>
+      </c>
+      <c r="G9">
+        <v>4.78</v>
+      </c>
+      <c r="H9">
+        <v>11.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2.45</v>
+      </c>
+      <c r="K9">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L9">
+        <v>1.526</v>
+      </c>
+      <c r="M9">
+        <v>0.06467643000000002</v>
+      </c>
+      <c r="N9">
+        <v>1.46132357</v>
+      </c>
+      <c r="O9">
+        <v>0.3507176568000001</v>
+      </c>
+      <c r="P9">
+        <v>1.1106059132</v>
+      </c>
+      <c r="Q9">
+        <v>2.0346059132</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09621266619271784</v>
+      </c>
+      <c r="T9">
+        <v>0.9036667355020065</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.033972</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>23.59437588005398</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09167720486542964</v>
+      </c>
+      <c r="C10">
+        <v>19.00203000668778</v>
+      </c>
+      <c r="D10">
+        <v>15.87563000668777</v>
+      </c>
+      <c r="E10">
+        <v>-7.716399999999999</v>
+      </c>
+      <c r="F10">
+        <v>1.6536</v>
+      </c>
+      <c r="G10">
+        <v>4.78</v>
+      </c>
+      <c r="H10">
+        <v>11.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2.45</v>
+      </c>
+      <c r="K10">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L10">
+        <v>1.526</v>
+      </c>
+      <c r="M10">
+        <v>0.07391592000000001</v>
+      </c>
+      <c r="N10">
+        <v>1.45208408</v>
+      </c>
+      <c r="O10">
+        <v>0.3485001792000001</v>
+      </c>
+      <c r="P10">
+        <v>1.1035839008</v>
+      </c>
+      <c r="Q10">
+        <v>2.0275839008</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09669504876677135</v>
+      </c>
+      <c r="T10">
+        <v>0.911259364705025</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.033972</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>20.64507889504724</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.0914985901716317</v>
+      </c>
+      <c r="C11">
+        <v>18.84913829232234</v>
+      </c>
+      <c r="D11">
+        <v>15.92943829232234</v>
+      </c>
+      <c r="E11">
+        <v>-7.509699999999999</v>
+      </c>
+      <c r="F11">
+        <v>1.8603</v>
+      </c>
+      <c r="G11">
+        <v>4.78</v>
+      </c>
+      <c r="H11">
+        <v>11.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2.45</v>
+      </c>
+      <c r="K11">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L11">
+        <v>1.526</v>
+      </c>
+      <c r="M11">
+        <v>0.08315541000000001</v>
+      </c>
+      <c r="N11">
+        <v>1.44284459</v>
+      </c>
+      <c r="O11">
+        <v>0.3462827016</v>
+      </c>
+      <c r="P11">
+        <v>1.0965618884</v>
+      </c>
+      <c r="Q11">
+        <v>2.0205618884</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09718803315563923</v>
+      </c>
+      <c r="T11">
+        <v>0.9190188648795385</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.033972</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>18.35118124004199</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09131997547783376</v>
+      </c>
+      <c r="C12">
+        <v>18.69661257014844</v>
+      </c>
+      <c r="D12">
+        <v>15.98361257014844</v>
+      </c>
+      <c r="E12">
+        <v>-7.302999999999999</v>
+      </c>
+      <c r="F12">
+        <v>2.067</v>
+      </c>
+      <c r="G12">
+        <v>4.78</v>
+      </c>
+      <c r="H12">
+        <v>11.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>2.45</v>
+      </c>
+      <c r="K12">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L12">
+        <v>1.526</v>
+      </c>
+      <c r="M12">
+        <v>0.09239490000000002</v>
+      </c>
+      <c r="N12">
+        <v>1.4336051</v>
+      </c>
+      <c r="O12">
+        <v>0.3440652240000001</v>
+      </c>
+      <c r="P12">
+        <v>1.089539876</v>
+      </c>
+      <c r="Q12">
+        <v>2.013539876</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09769197275314861</v>
+      </c>
+      <c r="T12">
+        <v>0.9269507983912636</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.033972</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>16.51606311603779</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.0911413607840358</v>
+      </c>
+      <c r="C13">
+        <v>18.54445658700696</v>
+      </c>
+      <c r="D13">
+        <v>16.03815658700696</v>
+      </c>
+      <c r="E13">
+        <v>-7.096299999999999</v>
+      </c>
+      <c r="F13">
+        <v>2.2737</v>
+      </c>
+      <c r="G13">
+        <v>4.78</v>
+      </c>
+      <c r="H13">
+        <v>11.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2.45</v>
+      </c>
+      <c r="K13">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L13">
+        <v>1.526</v>
+      </c>
+      <c r="M13">
+        <v>0.10163439</v>
+      </c>
+      <c r="N13">
+        <v>1.42436561</v>
+      </c>
+      <c r="O13">
+        <v>0.3418477464</v>
+      </c>
+      <c r="P13">
+        <v>1.0825178636</v>
+      </c>
+      <c r="Q13">
+        <v>2.0065178636</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09820723683599528</v>
+      </c>
+      <c r="T13">
+        <v>0.9350609775998812</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.033972</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>15.01460283276163</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09096274609023784</v>
+      </c>
+      <c r="C14">
+        <v>18.39267414105821</v>
+      </c>
+      <c r="D14">
+        <v>16.09307414105821</v>
+      </c>
+      <c r="E14">
+        <v>-6.8896</v>
+      </c>
+      <c r="F14">
+        <v>2.4804</v>
+      </c>
+      <c r="G14">
+        <v>4.78</v>
+      </c>
+      <c r="H14">
+        <v>11.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2.45</v>
+      </c>
+      <c r="K14">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L14">
+        <v>1.526</v>
+      </c>
+      <c r="M14">
+        <v>0.11087388</v>
+      </c>
+      <c r="N14">
+        <v>1.41512612</v>
+      </c>
+      <c r="O14">
+        <v>0.3396302688</v>
+      </c>
+      <c r="P14">
+        <v>1.0754958512</v>
+      </c>
+      <c r="Q14">
+        <v>1.9994958512</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09873421146617936</v>
+      </c>
+      <c r="T14">
+        <v>0.94335547906324</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.033972</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>13.76338593003149</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09089281139643988</v>
+      </c>
+      <c r="C15">
+        <v>18.207579122286</v>
+      </c>
+      <c r="D15">
+        <v>16.114679122286</v>
+      </c>
+      <c r="E15">
+        <v>-6.682899999999998</v>
+      </c>
+      <c r="F15">
+        <v>2.6871</v>
+      </c>
+      <c r="G15">
+        <v>4.78</v>
+      </c>
+      <c r="H15">
+        <v>11.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2.45</v>
+      </c>
+      <c r="K15">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L15">
+        <v>1.526</v>
+      </c>
+      <c r="M15">
+        <v>0.12306918</v>
+      </c>
+      <c r="N15">
+        <v>1.40293082</v>
+      </c>
+      <c r="O15">
+        <v>0.3367033968</v>
+      </c>
+      <c r="P15">
+        <v>1.0662274232</v>
+      </c>
+      <c r="Q15">
+        <v>1.9902274232</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09927330045567803</v>
+      </c>
+      <c r="T15">
+        <v>0.951840658721159</v>
+      </c>
+      <c r="U15">
+        <v>0.0458</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.034808</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>12.3995300854365</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09072255670264193</v>
+      </c>
+      <c r="C16">
+        <v>18.05371935076953</v>
+      </c>
+      <c r="D16">
+        <v>16.16751935076953</v>
+      </c>
+      <c r="E16">
+        <v>-6.476199999999999</v>
+      </c>
+      <c r="F16">
+        <v>2.893800000000001</v>
+      </c>
+      <c r="G16">
+        <v>4.78</v>
+      </c>
+      <c r="H16">
+        <v>11.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2.45</v>
+      </c>
+      <c r="K16">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L16">
+        <v>1.526</v>
+      </c>
+      <c r="M16">
+        <v>0.13253604</v>
+      </c>
+      <c r="N16">
+        <v>1.39346396</v>
+      </c>
+      <c r="O16">
+        <v>0.3344313504</v>
+      </c>
+      <c r="P16">
+        <v>1.0590326096</v>
+      </c>
+      <c r="Q16">
+        <v>1.9830326096</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09982492639842086</v>
+      </c>
+      <c r="T16">
+        <v>0.9605231681385643</v>
+      </c>
+      <c r="U16">
+        <v>0.0458</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.034808</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>11.51384936504818</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09055230200884397</v>
+      </c>
+      <c r="C17">
+        <v>17.90020724676047</v>
+      </c>
+      <c r="D17">
+        <v>16.22070724676047</v>
+      </c>
+      <c r="E17">
+        <v>-6.269499999999999</v>
+      </c>
+      <c r="F17">
+        <v>3.1005</v>
+      </c>
+      <c r="G17">
+        <v>4.78</v>
+      </c>
+      <c r="H17">
+        <v>11.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2.45</v>
+      </c>
+      <c r="K17">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L17">
+        <v>1.526</v>
+      </c>
+      <c r="M17">
+        <v>0.1420029</v>
+      </c>
+      <c r="N17">
+        <v>1.3839971</v>
+      </c>
+      <c r="O17">
+        <v>0.332159304</v>
+      </c>
+      <c r="P17">
+        <v>1.051837796</v>
+      </c>
+      <c r="Q17">
+        <v>1.975837796</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1003895317751106</v>
+      </c>
+      <c r="T17">
+        <v>0.9694099718952027</v>
+      </c>
+      <c r="U17">
+        <v>0.0458</v>
+      </c>
+      <c r="V17">
+        <v>0.24</v>
+      </c>
+      <c r="W17">
+        <v>0.034808</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>10.7462594073783</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09038204731504604</v>
+      </c>
+      <c r="C18">
+        <v>17.74704625285334</v>
+      </c>
+      <c r="D18">
+        <v>16.27424625285334</v>
+      </c>
+      <c r="E18">
+        <v>-6.062799999999999</v>
+      </c>
+      <c r="F18">
+        <v>3.3072</v>
+      </c>
+      <c r="G18">
+        <v>4.78</v>
+      </c>
+      <c r="H18">
+        <v>11.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2.45</v>
+      </c>
+      <c r="K18">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L18">
+        <v>1.526</v>
+      </c>
+      <c r="M18">
+        <v>0.15146976</v>
+      </c>
+      <c r="N18">
+        <v>1.37453024</v>
+      </c>
+      <c r="O18">
+        <v>0.3298872576000001</v>
+      </c>
+      <c r="P18">
+        <v>1.0446429824</v>
+      </c>
+      <c r="Q18">
+        <v>1.9686429824</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1009675801369596</v>
+      </c>
+      <c r="T18">
+        <v>0.9785083662174756</v>
+      </c>
+      <c r="U18">
+        <v>0.0458</v>
+      </c>
+      <c r="V18">
+        <v>0.24</v>
+      </c>
+      <c r="W18">
+        <v>0.034808</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>10.07461819441716</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09049603262124808</v>
+      </c>
+      <c r="C19">
+        <v>17.50446293940974</v>
+      </c>
+      <c r="D19">
+        <v>16.23836293940974</v>
+      </c>
+      <c r="E19">
+        <v>-5.856099999999999</v>
+      </c>
+      <c r="F19">
+        <v>3.5139</v>
+      </c>
+      <c r="G19">
+        <v>4.78</v>
+      </c>
+      <c r="H19">
+        <v>11.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2.45</v>
+      </c>
+      <c r="K19">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L19">
+        <v>1.526</v>
+      </c>
+      <c r="M19">
+        <v>0.1686672</v>
+      </c>
+      <c r="N19">
+        <v>1.3573328</v>
+      </c>
+      <c r="O19">
+        <v>0.3257598720000001</v>
+      </c>
+      <c r="P19">
+        <v>1.031572928</v>
+      </c>
+      <c r="Q19">
+        <v>1.955572928</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1015595573749977</v>
+      </c>
+      <c r="T19">
+        <v>0.9878259989571524</v>
+      </c>
+      <c r="U19">
+        <v>0.048</v>
+      </c>
+      <c r="V19">
+        <v>0.24</v>
+      </c>
+      <c r="W19">
+        <v>0.03648</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>9.047402221653055</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09034249792745014</v>
+      </c>
+      <c r="C20">
+        <v>17.34613374373496</v>
+      </c>
+      <c r="D20">
+        <v>16.28673374373496</v>
+      </c>
+      <c r="E20">
+        <v>-5.649399999999999</v>
+      </c>
+      <c r="F20">
+        <v>3.7206</v>
+      </c>
+      <c r="G20">
+        <v>4.78</v>
+      </c>
+      <c r="H20">
+        <v>11.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2.45</v>
+      </c>
+      <c r="K20">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L20">
+        <v>1.526</v>
+      </c>
+      <c r="M20">
+        <v>0.1785888</v>
+      </c>
+      <c r="N20">
+        <v>1.3474112</v>
+      </c>
+      <c r="O20">
+        <v>0.323378688</v>
+      </c>
+      <c r="P20">
+        <v>1.024032512</v>
+      </c>
+      <c r="Q20">
+        <v>1.948032512</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1021659730822563</v>
+      </c>
+      <c r="T20">
+        <v>0.9973708910319432</v>
+      </c>
+      <c r="U20">
+        <v>0.048</v>
+      </c>
+      <c r="V20">
+        <v>0.24</v>
+      </c>
+      <c r="W20">
+        <v>0.03648</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>8.544768764894553</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09018896323365218</v>
+      </c>
+      <c r="C21">
+        <v>17.18809358275417</v>
+      </c>
+      <c r="D21">
+        <v>16.33539358275417</v>
+      </c>
+      <c r="E21">
+        <v>-5.442699999999999</v>
+      </c>
+      <c r="F21">
+        <v>3.9273</v>
+      </c>
+      <c r="G21">
+        <v>4.78</v>
+      </c>
+      <c r="H21">
+        <v>11.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2.45</v>
+      </c>
+      <c r="K21">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L21">
+        <v>1.526</v>
+      </c>
+      <c r="M21">
+        <v>0.1885104</v>
+      </c>
+      <c r="N21">
+        <v>1.3374896</v>
+      </c>
+      <c r="O21">
+        <v>0.320997504</v>
+      </c>
+      <c r="P21">
+        <v>1.016492096</v>
+      </c>
+      <c r="Q21">
+        <v>1.940492096</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1027873620168545</v>
+      </c>
+      <c r="T21">
+        <v>1.00715145945426</v>
+      </c>
+      <c r="U21">
+        <v>0.048</v>
+      </c>
+      <c r="V21">
+        <v>0.24</v>
+      </c>
+      <c r="W21">
+        <v>0.03648</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>8.095044093057997</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09026342853985422</v>
+      </c>
+      <c r="C22">
+        <v>16.95775699033148</v>
+      </c>
+      <c r="D22">
+        <v>16.31175699033148</v>
+      </c>
+      <c r="E22">
+        <v>-5.235999999999999</v>
+      </c>
+      <c r="F22">
+        <v>4.134</v>
+      </c>
+      <c r="G22">
+        <v>4.78</v>
+      </c>
+      <c r="H22">
+        <v>11.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2.45</v>
+      </c>
+      <c r="K22">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L22">
+        <v>1.526</v>
+      </c>
+      <c r="M22">
+        <v>0.204633</v>
+      </c>
+      <c r="N22">
+        <v>1.321367</v>
+      </c>
+      <c r="O22">
+        <v>0.31712808</v>
+      </c>
+      <c r="P22">
+        <v>1.00423892</v>
+      </c>
+      <c r="Q22">
+        <v>1.92823892</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1034242856748178</v>
+      </c>
+      <c r="T22">
+        <v>1.017176542087134</v>
+      </c>
+      <c r="U22">
+        <v>0.0495</v>
+      </c>
+      <c r="V22">
+        <v>0.24</v>
+      </c>
+      <c r="W22">
+        <v>0.03762</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>7.457252740271608</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09012129384605627</v>
+      </c>
+      <c r="C23">
+        <v>16.79623251907169</v>
+      </c>
+      <c r="D23">
+        <v>16.35693251907169</v>
+      </c>
+      <c r="E23">
+        <v>-5.029299999999999</v>
+      </c>
+      <c r="F23">
+        <v>4.3407</v>
+      </c>
+      <c r="G23">
+        <v>4.78</v>
+      </c>
+      <c r="H23">
+        <v>11.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2.45</v>
+      </c>
+      <c r="K23">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L23">
+        <v>1.526</v>
+      </c>
+      <c r="M23">
+        <v>0.21486465</v>
+      </c>
+      <c r="N23">
+        <v>1.31113535</v>
+      </c>
+      <c r="O23">
+        <v>0.314672484</v>
+      </c>
+      <c r="P23">
+        <v>0.9964628660000002</v>
+      </c>
+      <c r="Q23">
+        <v>1.920462866</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1040773339823497</v>
+      </c>
+      <c r="T23">
+        <v>1.027455424280335</v>
+      </c>
+      <c r="U23">
+        <v>0.0495</v>
+      </c>
+      <c r="V23">
+        <v>0.24</v>
+      </c>
+      <c r="W23">
+        <v>0.03762</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>7.102145466925342</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08997915915225833</v>
+      </c>
+      <c r="C24">
+        <v>16.63495897065046</v>
+      </c>
+      <c r="D24">
+        <v>16.40235897065045</v>
+      </c>
+      <c r="E24">
+        <v>-4.822599999999999</v>
+      </c>
+      <c r="F24">
+        <v>4.547400000000001</v>
+      </c>
+      <c r="G24">
+        <v>4.78</v>
+      </c>
+      <c r="H24">
+        <v>11.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2.45</v>
+      </c>
+      <c r="K24">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L24">
+        <v>1.526</v>
+      </c>
+      <c r="M24">
+        <v>0.2250963</v>
+      </c>
+      <c r="N24">
+        <v>1.3009037</v>
+      </c>
+      <c r="O24">
+        <v>0.312216888</v>
+      </c>
+      <c r="P24">
+        <v>0.9886868120000001</v>
+      </c>
+      <c r="Q24">
+        <v>1.912686812</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1047471271182799</v>
+      </c>
+      <c r="T24">
+        <v>1.037997867555412</v>
+      </c>
+      <c r="U24">
+        <v>0.0495</v>
+      </c>
+      <c r="V24">
+        <v>0.24</v>
+      </c>
+      <c r="W24">
+        <v>0.03762</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>6.779320672974189</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08983702445846037</v>
+      </c>
+      <c r="C25">
+        <v>16.47393844147766</v>
+      </c>
+      <c r="D25">
+        <v>16.44803844147766</v>
+      </c>
+      <c r="E25">
+        <v>-4.615899999999999</v>
+      </c>
+      <c r="F25">
+        <v>4.7541</v>
+      </c>
+      <c r="G25">
+        <v>4.78</v>
+      </c>
+      <c r="H25">
+        <v>11.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2.45</v>
+      </c>
+      <c r="K25">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L25">
+        <v>1.526</v>
+      </c>
+      <c r="M25">
+        <v>0.23532795</v>
+      </c>
+      <c r="N25">
+        <v>1.29067205</v>
+      </c>
+      <c r="O25">
+        <v>0.309761292</v>
+      </c>
+      <c r="P25">
+        <v>0.9809107580000002</v>
+      </c>
+      <c r="Q25">
+        <v>1.904910758</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.10543431747852</v>
+      </c>
+      <c r="T25">
+        <v>1.048814140525946</v>
+      </c>
+      <c r="U25">
+        <v>0.0495</v>
+      </c>
+      <c r="V25">
+        <v>0.24</v>
+      </c>
+      <c r="W25">
+        <v>0.03762</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>6.484567600236182</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08969488976466242</v>
+      </c>
+      <c r="C26">
+        <v>16.31317305138185</v>
+      </c>
+      <c r="D26">
+        <v>16.49397305138185</v>
+      </c>
+      <c r="E26">
+        <v>-4.409199999999999</v>
+      </c>
+      <c r="F26">
+        <v>4.9608</v>
+      </c>
+      <c r="G26">
+        <v>4.78</v>
+      </c>
+      <c r="H26">
+        <v>11.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2.45</v>
+      </c>
+      <c r="K26">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L26">
+        <v>1.526</v>
+      </c>
+      <c r="M26">
+        <v>0.2455596</v>
+      </c>
+      <c r="N26">
+        <v>1.2804404</v>
+      </c>
+      <c r="O26">
+        <v>0.3073056960000001</v>
+      </c>
+      <c r="P26">
+        <v>0.9731347040000002</v>
+      </c>
+      <c r="Q26">
+        <v>1.897134704</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1061395917956084</v>
+      </c>
+      <c r="T26">
+        <v>1.059915052258863</v>
+      </c>
+      <c r="U26">
+        <v>0.0495</v>
+      </c>
+      <c r="V26">
+        <v>0.24</v>
+      </c>
+      <c r="W26">
+        <v>0.03762</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>6.214377283559674</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08981875507086447</v>
+      </c>
+      <c r="C27">
+        <v>16.06642834586796</v>
+      </c>
+      <c r="D27">
+        <v>16.45392834586796</v>
+      </c>
+      <c r="E27">
+        <v>-4.202499999999999</v>
+      </c>
+      <c r="F27">
+        <v>5.1675</v>
+      </c>
+      <c r="G27">
+        <v>4.78</v>
+      </c>
+      <c r="H27">
+        <v>11.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2.45</v>
+      </c>
+      <c r="K27">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L27">
+        <v>1.526</v>
+      </c>
+      <c r="M27">
+        <v>0.26302575</v>
+      </c>
+      <c r="N27">
+        <v>1.26297425</v>
+      </c>
+      <c r="O27">
+        <v>0.30311382</v>
+      </c>
+      <c r="P27">
+        <v>0.9598604300000002</v>
+      </c>
+      <c r="Q27">
+        <v>1.88386043</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1068636734278193</v>
+      </c>
+      <c r="T27">
+        <v>1.071311988304657</v>
+      </c>
+      <c r="U27">
+        <v>0.0509</v>
+      </c>
+      <c r="V27">
+        <v>0.24</v>
+      </c>
+      <c r="W27">
+        <v>0.038684</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.801713330348836</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08968726037706651</v>
+      </c>
+      <c r="C28">
+        <v>15.90224594759345</v>
+      </c>
+      <c r="D28">
+        <v>16.49644594759345</v>
+      </c>
+      <c r="E28">
+        <v>-3.995799999999998</v>
+      </c>
+      <c r="F28">
+        <v>5.374200000000001</v>
+      </c>
+      <c r="G28">
+        <v>4.78</v>
+      </c>
+      <c r="H28">
+        <v>11.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2.45</v>
+      </c>
+      <c r="K28">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L28">
+        <v>1.526</v>
+      </c>
+      <c r="M28">
+        <v>0.27354678</v>
+      </c>
+      <c r="N28">
+        <v>1.25245322</v>
+      </c>
+      <c r="O28">
+        <v>0.3005887728000001</v>
+      </c>
+      <c r="P28">
+        <v>0.9518644472000002</v>
+      </c>
+      <c r="Q28">
+        <v>1.8758644472</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1076073248338737</v>
+      </c>
+      <c r="T28">
+        <v>1.083016949648986</v>
+      </c>
+      <c r="U28">
+        <v>0.0509</v>
+      </c>
+      <c r="V28">
+        <v>0.24</v>
+      </c>
+      <c r="W28">
+        <v>0.038684</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.578570509950803</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08955576568326856</v>
+      </c>
+      <c r="C29">
+        <v>15.73828385292168</v>
+      </c>
+      <c r="D29">
+        <v>16.53918385292168</v>
+      </c>
+      <c r="E29">
+        <v>-3.789099999999999</v>
+      </c>
+      <c r="F29">
+        <v>5.580900000000001</v>
+      </c>
+      <c r="G29">
+        <v>4.78</v>
+      </c>
+      <c r="H29">
+        <v>11.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2.45</v>
+      </c>
+      <c r="K29">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L29">
+        <v>1.526</v>
+      </c>
+      <c r="M29">
+        <v>0.28406781</v>
+      </c>
+      <c r="N29">
+        <v>1.24193219</v>
+      </c>
+      <c r="O29">
+        <v>0.2980637256000001</v>
+      </c>
+      <c r="P29">
+        <v>0.9438684644000002</v>
+      </c>
+      <c r="Q29">
+        <v>1.8678684644</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1083713502510528</v>
+      </c>
+      <c r="T29">
+        <v>1.095042594865763</v>
+      </c>
+      <c r="U29">
+        <v>0.0509</v>
+      </c>
+      <c r="V29">
+        <v>0.24</v>
+      </c>
+      <c r="W29">
+        <v>0.038684</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.371956787360032</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.0894242709894706</v>
+      </c>
+      <c r="C30">
+        <v>15.57454377854432</v>
+      </c>
+      <c r="D30">
+        <v>16.58214377854432</v>
+      </c>
+      <c r="E30">
+        <v>-3.582399999999998</v>
+      </c>
+      <c r="F30">
+        <v>5.787600000000001</v>
+      </c>
+      <c r="G30">
+        <v>4.78</v>
+      </c>
+      <c r="H30">
+        <v>11.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2.45</v>
+      </c>
+      <c r="K30">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L30">
+        <v>1.526</v>
+      </c>
+      <c r="M30">
+        <v>0.2945888400000001</v>
+      </c>
+      <c r="N30">
+        <v>1.23141116</v>
+      </c>
+      <c r="O30">
+        <v>0.2955386784</v>
+      </c>
+      <c r="P30">
+        <v>0.9358724816000001</v>
+      </c>
+      <c r="Q30">
+        <v>1.8598724816</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.109156598596487</v>
+      </c>
+      <c r="T30">
+        <v>1.107402285783005</v>
+      </c>
+      <c r="U30">
+        <v>0.0509</v>
+      </c>
+      <c r="V30">
+        <v>0.24</v>
+      </c>
+      <c r="W30">
+        <v>0.038684</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.180101187811459</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08929277629567266</v>
+      </c>
+      <c r="C31">
+        <v>15.41102745903567</v>
+      </c>
+      <c r="D31">
+        <v>16.62532745903566</v>
+      </c>
+      <c r="E31">
+        <v>-3.375699999999999</v>
+      </c>
+      <c r="F31">
+        <v>5.9943</v>
+      </c>
+      <c r="G31">
+        <v>4.78</v>
+      </c>
+      <c r="H31">
+        <v>11.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2.45</v>
+      </c>
+      <c r="K31">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L31">
+        <v>1.526</v>
+      </c>
+      <c r="M31">
+        <v>0.30510987</v>
+      </c>
+      <c r="N31">
+        <v>1.22089013</v>
+      </c>
+      <c r="O31">
+        <v>0.2930136312000001</v>
+      </c>
+      <c r="P31">
+        <v>0.9278764988000003</v>
+      </c>
+      <c r="Q31">
+        <v>1.8518764988</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1099639666136235</v>
+      </c>
+      <c r="T31">
+        <v>1.120110137007776</v>
+      </c>
+      <c r="U31">
+        <v>0.0509</v>
+      </c>
+      <c r="V31">
+        <v>0.24</v>
+      </c>
+      <c r="W31">
+        <v>0.038684</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>5.001477008921411</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.0891612816018747</v>
+      </c>
+      <c r="C32">
+        <v>15.2477366470861</v>
+      </c>
+      <c r="D32">
+        <v>16.6687366470861</v>
+      </c>
+      <c r="E32">
+        <v>-3.168999999999999</v>
+      </c>
+      <c r="F32">
+        <v>6.201000000000001</v>
+      </c>
+      <c r="G32">
+        <v>4.78</v>
+      </c>
+      <c r="H32">
+        <v>11.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2.45</v>
+      </c>
+      <c r="K32">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L32">
+        <v>1.526</v>
+      </c>
+      <c r="M32">
+        <v>0.3156309</v>
+      </c>
+      <c r="N32">
+        <v>1.2103691</v>
+      </c>
+      <c r="O32">
+        <v>0.290488584</v>
+      </c>
+      <c r="P32">
+        <v>0.9198805160000003</v>
+      </c>
+      <c r="Q32">
+        <v>1.843880516</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1107944022883924</v>
+      </c>
+      <c r="T32">
+        <v>1.133181069696111</v>
+      </c>
+      <c r="U32">
+        <v>0.0509</v>
+      </c>
+      <c r="V32">
+        <v>0.24</v>
+      </c>
+      <c r="W32">
+        <v>0.038684</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.834761108624029</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08902978690807674</v>
+      </c>
+      <c r="C33">
+        <v>15.08467311373922</v>
+      </c>
+      <c r="D33">
+        <v>16.71237311373921</v>
+      </c>
+      <c r="E33">
+        <v>-2.962299999999999</v>
+      </c>
+      <c r="F33">
+        <v>6.4077</v>
+      </c>
+      <c r="G33">
+        <v>4.78</v>
+      </c>
+      <c r="H33">
+        <v>11.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>2.45</v>
+      </c>
+      <c r="K33">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L33">
+        <v>1.526</v>
+      </c>
+      <c r="M33">
+        <v>0.32615193</v>
+      </c>
+      <c r="N33">
+        <v>1.19984807</v>
+      </c>
+      <c r="O33">
+        <v>0.2879635368</v>
+      </c>
+      <c r="P33">
+        <v>0.9118845332000003</v>
+      </c>
+      <c r="Q33">
+        <v>1.8358845332</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1116489085624301</v>
+      </c>
+      <c r="T33">
+        <v>1.146630869998601</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.24</v>
+      </c>
+      <c r="W33">
+        <v>0.038684</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.678801072861964</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08889829221427881</v>
+      </c>
+      <c r="C34">
+        <v>14.92183864863267</v>
+      </c>
+      <c r="D34">
+        <v>16.75623864863267</v>
+      </c>
+      <c r="E34">
+        <v>-2.755599999999998</v>
+      </c>
+      <c r="F34">
+        <v>6.614400000000001</v>
+      </c>
+      <c r="G34">
+        <v>4.78</v>
+      </c>
+      <c r="H34">
+        <v>11.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>2.45</v>
+      </c>
+      <c r="K34">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L34">
+        <v>1.526</v>
+      </c>
+      <c r="M34">
+        <v>0.33667296</v>
+      </c>
+      <c r="N34">
+        <v>1.18932704</v>
+      </c>
+      <c r="O34">
+        <v>0.2854384896000001</v>
+      </c>
+      <c r="P34">
+        <v>0.9038885504000002</v>
+      </c>
+      <c r="Q34">
+        <v>1.8278885504</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1125285473739394</v>
+      </c>
+      <c r="T34">
+        <v>1.16047625266293</v>
+      </c>
+      <c r="U34">
+        <v>0.0509</v>
+      </c>
+      <c r="V34">
+        <v>0.24</v>
+      </c>
+      <c r="W34">
+        <v>0.038684</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.532588539335027</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08941887752048086</v>
+      </c>
+      <c r="C35">
+        <v>14.54281061500206</v>
+      </c>
+      <c r="D35">
+        <v>16.58391061500206</v>
+      </c>
+      <c r="E35">
+        <v>-2.548899999999998</v>
+      </c>
+      <c r="F35">
+        <v>6.821100000000001</v>
+      </c>
+      <c r="G35">
+        <v>4.78</v>
+      </c>
+      <c r="H35">
+        <v>11.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2.45</v>
+      </c>
+      <c r="K35">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L35">
+        <v>1.526</v>
+      </c>
+      <c r="M35">
+        <v>0.3649288500000001</v>
+      </c>
+      <c r="N35">
+        <v>1.16107115</v>
+      </c>
+      <c r="O35">
+        <v>0.278657076</v>
+      </c>
+      <c r="P35">
+        <v>0.8824140740000002</v>
+      </c>
+      <c r="Q35">
+        <v>1.806414074</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1134344440604192</v>
+      </c>
+      <c r="T35">
+        <v>1.174734930332163</v>
+      </c>
+      <c r="U35">
+        <v>0.0535</v>
+      </c>
+      <c r="V35">
+        <v>0.24</v>
+      </c>
+      <c r="W35">
+        <v>0.04066</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.181637050619593</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08930714282668289</v>
+      </c>
+      <c r="C36">
+        <v>14.37279845895512</v>
+      </c>
+      <c r="D36">
+        <v>16.62059845895512</v>
+      </c>
+      <c r="E36">
+        <v>-2.342199999999998</v>
+      </c>
+      <c r="F36">
+        <v>7.027800000000001</v>
+      </c>
+      <c r="G36">
+        <v>4.78</v>
+      </c>
+      <c r="H36">
+        <v>11.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2.45</v>
+      </c>
+      <c r="K36">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L36">
+        <v>1.526</v>
+      </c>
+      <c r="M36">
+        <v>0.3759873</v>
+      </c>
+      <c r="N36">
+        <v>1.1500127</v>
+      </c>
+      <c r="O36">
+        <v>0.276003048</v>
+      </c>
+      <c r="P36">
+        <v>0.8740096520000002</v>
+      </c>
+      <c r="Q36">
+        <v>1.798009652</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1143677921616408</v>
+      </c>
+      <c r="T36">
+        <v>1.189425689142888</v>
+      </c>
+      <c r="U36">
+        <v>0.0535</v>
+      </c>
+      <c r="V36">
+        <v>0.24</v>
+      </c>
+      <c r="W36">
+        <v>0.04066</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.05864772560137</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08991360813288495</v>
+      </c>
+      <c r="C37">
+        <v>13.96889429548722</v>
+      </c>
+      <c r="D37">
+        <v>16.42339429548722</v>
+      </c>
+      <c r="E37">
+        <v>-2.135499999999998</v>
+      </c>
+      <c r="F37">
+        <v>7.234500000000001</v>
+      </c>
+      <c r="G37">
+        <v>4.78</v>
+      </c>
+      <c r="H37">
+        <v>11.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2.45</v>
+      </c>
+      <c r="K37">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L37">
+        <v>1.526</v>
+      </c>
+      <c r="M37">
+        <v>0.4065789000000001</v>
+      </c>
+      <c r="N37">
+        <v>1.1194211</v>
+      </c>
+      <c r="O37">
+        <v>0.2686610640000001</v>
+      </c>
+      <c r="P37">
+        <v>0.8507600360000003</v>
+      </c>
+      <c r="Q37">
+        <v>1.774760036</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1153298586659769</v>
+      </c>
+      <c r="T37">
+        <v>1.204568471301636</v>
+      </c>
+      <c r="U37">
+        <v>0.0562</v>
+      </c>
+      <c r="V37">
+        <v>0.24</v>
+      </c>
+      <c r="W37">
+        <v>0.042712</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.753269045688303</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08982239343908699</v>
+      </c>
+      <c r="C38">
+        <v>13.79155502870281</v>
+      </c>
+      <c r="D38">
+        <v>16.45275502870281</v>
+      </c>
+      <c r="E38">
+        <v>-1.928799999999999</v>
+      </c>
+      <c r="F38">
+        <v>7.4412</v>
+      </c>
+      <c r="G38">
+        <v>4.78</v>
+      </c>
+      <c r="H38">
+        <v>11.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2.45</v>
+      </c>
+      <c r="K38">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L38">
+        <v>1.526</v>
+      </c>
+      <c r="M38">
+        <v>0.41819544</v>
+      </c>
+      <c r="N38">
+        <v>1.10780456</v>
+      </c>
+      <c r="O38">
+        <v>0.2658730944</v>
+      </c>
+      <c r="P38">
+        <v>0.8419314656000001</v>
+      </c>
+      <c r="Q38">
+        <v>1.7659314656</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1163219897485734</v>
+      </c>
+      <c r="T38">
+        <v>1.220184465402844</v>
+      </c>
+      <c r="U38">
+        <v>0.0562</v>
+      </c>
+      <c r="V38">
+        <v>0.24</v>
+      </c>
+      <c r="W38">
+        <v>0.042712</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>3.649011572196962</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08973117874528905</v>
+      </c>
+      <c r="C39">
+        <v>13.61432092855133</v>
+      </c>
+      <c r="D39">
+        <v>16.48222092855133</v>
+      </c>
+      <c r="E39">
+        <v>-1.722099999999998</v>
+      </c>
+      <c r="F39">
+        <v>7.647900000000001</v>
+      </c>
+      <c r="G39">
+        <v>4.78</v>
+      </c>
+      <c r="H39">
+        <v>11.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2.45</v>
+      </c>
+      <c r="K39">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L39">
+        <v>1.526</v>
+      </c>
+      <c r="M39">
+        <v>0.42981198</v>
+      </c>
+      <c r="N39">
+        <v>1.09618802</v>
+      </c>
+      <c r="O39">
+        <v>0.2630851248000001</v>
+      </c>
+      <c r="P39">
+        <v>0.8331028952000001</v>
+      </c>
+      <c r="Q39">
+        <v>1.7571028952</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1173456170560144</v>
+      </c>
+      <c r="T39">
+        <v>1.236296205348535</v>
+      </c>
+      <c r="U39">
+        <v>0.0562</v>
+      </c>
+      <c r="V39">
+        <v>0.24</v>
+      </c>
+      <c r="W39">
+        <v>0.042712</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.55038963781326</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.09099732405149111</v>
+      </c>
+      <c r="C40">
+        <v>13.0078133322101</v>
+      </c>
+      <c r="D40">
+        <v>16.0824133322101</v>
+      </c>
+      <c r="E40">
+        <v>-1.515399999999999</v>
+      </c>
+      <c r="F40">
+        <v>7.8546</v>
+      </c>
+      <c r="G40">
+        <v>4.78</v>
+      </c>
+      <c r="H40">
+        <v>11.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2.45</v>
+      </c>
+      <c r="K40">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L40">
+        <v>1.526</v>
+      </c>
+      <c r="M40">
+        <v>0.4783451400000001</v>
+      </c>
+      <c r="N40">
+        <v>1.04765486</v>
+      </c>
+      <c r="O40">
+        <v>0.2514371664</v>
+      </c>
+      <c r="P40">
+        <v>0.7962176936000002</v>
+      </c>
+      <c r="Q40">
+        <v>1.7202176936</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1184022645991792</v>
+      </c>
+      <c r="T40">
+        <v>1.252927678840862</v>
+      </c>
+      <c r="U40">
+        <v>0.0609</v>
+      </c>
+      <c r="V40">
+        <v>0.24</v>
+      </c>
+      <c r="W40">
+        <v>0.04628400000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>3.190165159825811</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.09094182935769314</v>
+      </c>
+      <c r="C41">
+        <v>12.81822988938498</v>
+      </c>
+      <c r="D41">
+        <v>16.09952988938497</v>
+      </c>
+      <c r="E41">
+        <v>-1.308699999999998</v>
+      </c>
+      <c r="F41">
+        <v>8.061300000000001</v>
+      </c>
+      <c r="G41">
+        <v>4.78</v>
+      </c>
+      <c r="H41">
+        <v>11.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2.45</v>
+      </c>
+      <c r="K41">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L41">
+        <v>1.526</v>
+      </c>
+      <c r="M41">
+        <v>0.4909331700000001</v>
+      </c>
+      <c r="N41">
+        <v>1.03506683</v>
+      </c>
+      <c r="O41">
+        <v>0.2484160392</v>
+      </c>
+      <c r="P41">
+        <v>0.7866507908000001</v>
+      </c>
+      <c r="Q41">
+        <v>1.7106507908</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1194935563240871</v>
+      </c>
+      <c r="T41">
+        <v>1.270104446546051</v>
+      </c>
+      <c r="U41">
+        <v>0.0609</v>
+      </c>
+      <c r="V41">
+        <v>0.24</v>
+      </c>
+      <c r="W41">
+        <v>0.04628400000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.108366053163611</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.0908863346638952</v>
+      </c>
+      <c r="C42">
+        <v>12.62868291977706</v>
+      </c>
+      <c r="D42">
+        <v>16.11668291977706</v>
+      </c>
+      <c r="E42">
+        <v>-1.101999999999999</v>
+      </c>
+      <c r="F42">
+        <v>8.268000000000001</v>
+      </c>
+      <c r="G42">
+        <v>4.78</v>
+      </c>
+      <c r="H42">
+        <v>11.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2.45</v>
+      </c>
+      <c r="K42">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L42">
+        <v>1.526</v>
+      </c>
+      <c r="M42">
+        <v>0.5035212000000001</v>
+      </c>
+      <c r="N42">
+        <v>1.0224788</v>
+      </c>
+      <c r="O42">
+        <v>0.245394912</v>
+      </c>
+      <c r="P42">
+        <v>0.7770838880000001</v>
+      </c>
+      <c r="Q42">
+        <v>1.701083888</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1206212244398253</v>
+      </c>
+      <c r="T42">
+        <v>1.287853773174747</v>
+      </c>
+      <c r="U42">
+        <v>0.0609</v>
+      </c>
+      <c r="V42">
+        <v>0.24</v>
+      </c>
+      <c r="W42">
+        <v>0.04628400000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>3.03065690183452</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.09372871997009724</v>
+      </c>
+      <c r="C43">
+        <v>11.58799620497959</v>
+      </c>
+      <c r="D43">
+        <v>15.28269620497959</v>
+      </c>
+      <c r="E43">
+        <v>-0.8952999999999971</v>
+      </c>
+      <c r="F43">
+        <v>8.474700000000002</v>
+      </c>
+      <c r="G43">
+        <v>4.78</v>
+      </c>
+      <c r="H43">
+        <v>11.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>2.45</v>
+      </c>
+      <c r="K43">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L43">
+        <v>1.526</v>
+      </c>
+      <c r="M43">
+        <v>0.5949239400000002</v>
+      </c>
+      <c r="N43">
+        <v>0.9310760600000001</v>
+      </c>
+      <c r="O43">
+        <v>0.2234582544</v>
+      </c>
+      <c r="P43">
+        <v>0.7076178056000001</v>
+      </c>
+      <c r="Q43">
+        <v>1.6316178056</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1217871185933851</v>
+      </c>
+      <c r="T43">
+        <v>1.306204771892551</v>
+      </c>
+      <c r="U43">
+        <v>0.0702</v>
+      </c>
+      <c r="V43">
+        <v>0.24</v>
+      </c>
+      <c r="W43">
+        <v>0.053352</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.565033775578101</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.09374390527629929</v>
+      </c>
+      <c r="C44">
+        <v>11.37707239853011</v>
+      </c>
+      <c r="D44">
+        <v>15.27847239853011</v>
+      </c>
+      <c r="E44">
+        <v>-0.6885999999999992</v>
+      </c>
+      <c r="F44">
+        <v>8.6814</v>
+      </c>
+      <c r="G44">
+        <v>4.78</v>
+      </c>
+      <c r="H44">
+        <v>11.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>2.45</v>
+      </c>
+      <c r="K44">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L44">
+        <v>1.526</v>
+      </c>
+      <c r="M44">
+        <v>0.60943428</v>
+      </c>
+      <c r="N44">
+        <v>0.9165657200000003</v>
+      </c>
+      <c r="O44">
+        <v>0.2199757728000001</v>
+      </c>
+      <c r="P44">
+        <v>0.6965899472000002</v>
+      </c>
+      <c r="Q44">
+        <v>1.6205899472</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1229932159936195</v>
+      </c>
+      <c r="T44">
+        <v>1.32518856366959</v>
+      </c>
+      <c r="U44">
+        <v>0.0702</v>
+      </c>
+      <c r="V44">
+        <v>0.24</v>
+      </c>
+      <c r="W44">
+        <v>0.053352</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.503961542826243</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.09529505058250133</v>
+      </c>
+      <c r="C45">
+        <v>10.75088200950375</v>
+      </c>
+      <c r="D45">
+        <v>14.85898200950375</v>
+      </c>
+      <c r="E45">
+        <v>-0.4818999999999978</v>
+      </c>
+      <c r="F45">
+        <v>8.888100000000001</v>
+      </c>
+      <c r="G45">
+        <v>4.78</v>
+      </c>
+      <c r="H45">
+        <v>11.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>2.45</v>
+      </c>
+      <c r="K45">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L45">
+        <v>1.526</v>
+      </c>
+      <c r="M45">
+        <v>0.6657186900000001</v>
+      </c>
+      <c r="N45">
+        <v>0.8602813100000002</v>
+      </c>
+      <c r="O45">
+        <v>0.2064675144</v>
+      </c>
+      <c r="P45">
+        <v>0.6538137956000002</v>
+      </c>
+      <c r="Q45">
+        <v>1.5778137956</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1242416326008795</v>
+      </c>
+      <c r="T45">
+        <v>1.344838453403718</v>
+      </c>
+      <c r="U45">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V45">
+        <v>0.24</v>
+      </c>
+      <c r="W45">
+        <v>0.056924</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.292259512798116</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.09534595588870337</v>
+      </c>
+      <c r="C46">
+        <v>10.53080526103153</v>
+      </c>
+      <c r="D46">
+        <v>14.84560526103153</v>
+      </c>
+      <c r="E46">
+        <v>-0.2751999999999981</v>
+      </c>
+      <c r="F46">
+        <v>9.094800000000001</v>
+      </c>
+      <c r="G46">
+        <v>4.78</v>
+      </c>
+      <c r="H46">
+        <v>11.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2.45</v>
+      </c>
+      <c r="K46">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L46">
+        <v>1.526</v>
+      </c>
+      <c r="M46">
+        <v>0.68120052</v>
+      </c>
+      <c r="N46">
+        <v>0.8447994800000003</v>
+      </c>
+      <c r="O46">
+        <v>0.2027518752000001</v>
+      </c>
+      <c r="P46">
+        <v>0.6420476048000002</v>
+      </c>
+      <c r="Q46">
+        <v>1.5660476048</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1255346355155417</v>
+      </c>
+      <c r="T46">
+        <v>1.365190124914065</v>
+      </c>
+      <c r="U46">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V46">
+        <v>0.24</v>
+      </c>
+      <c r="W46">
+        <v>0.056924</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.240162705689068</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.09539686119490544</v>
+      </c>
+      <c r="C47">
+        <v>10.31075257564205</v>
+      </c>
+      <c r="D47">
+        <v>14.83225257564205</v>
+      </c>
+      <c r="E47">
+        <v>-0.06849999999999845</v>
+      </c>
+      <c r="F47">
+        <v>9.301500000000001</v>
+      </c>
+      <c r="G47">
+        <v>4.78</v>
+      </c>
+      <c r="H47">
+        <v>11.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>2.45</v>
+      </c>
+      <c r="K47">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L47">
+        <v>1.526</v>
+      </c>
+      <c r="M47">
+        <v>0.69668235</v>
+      </c>
+      <c r="N47">
+        <v>0.8293176500000002</v>
+      </c>
+      <c r="O47">
+        <v>0.1990362360000001</v>
+      </c>
+      <c r="P47">
+        <v>0.6302814140000002</v>
+      </c>
+      <c r="Q47">
+        <v>1.554281414</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1268746567180099</v>
+      </c>
+      <c r="T47">
+        <v>1.386281857206606</v>
+      </c>
+      <c r="U47">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V47">
+        <v>0.24</v>
+      </c>
+      <c r="W47">
+        <v>0.056924</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.190381312229311</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.09544776650110748</v>
+      </c>
+      <c r="C48">
+        <v>10.09072388846399</v>
+      </c>
+      <c r="D48">
+        <v>14.81892388846399</v>
+      </c>
+      <c r="E48">
+        <v>0.1382000000000012</v>
+      </c>
+      <c r="F48">
+        <v>9.5082</v>
+      </c>
+      <c r="G48">
+        <v>4.78</v>
+      </c>
+      <c r="H48">
+        <v>11.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2.45</v>
+      </c>
+      <c r="K48">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L48">
+        <v>1.526</v>
+      </c>
+      <c r="M48">
+        <v>0.7121641799999999</v>
+      </c>
+      <c r="N48">
+        <v>0.8138358200000003</v>
+      </c>
+      <c r="O48">
+        <v>0.1953205968000001</v>
+      </c>
+      <c r="P48">
+        <v>0.6185152232000002</v>
+      </c>
+      <c r="Q48">
+        <v>1.5425152232</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1282643083353842</v>
+      </c>
+      <c r="T48">
+        <v>1.408154764769242</v>
+      </c>
+      <c r="U48">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V48">
+        <v>0.24</v>
+      </c>
+      <c r="W48">
+        <v>0.056924</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.142764327180848</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.09549867180730953</v>
+      </c>
+      <c r="C49">
+        <v>9.870719134858982</v>
+      </c>
+      <c r="D49">
+        <v>14.80561913485898</v>
+      </c>
+      <c r="E49">
+        <v>0.3449000000000026</v>
+      </c>
+      <c r="F49">
+        <v>9.714900000000002</v>
+      </c>
+      <c r="G49">
+        <v>4.78</v>
+      </c>
+      <c r="H49">
+        <v>11.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2.45</v>
+      </c>
+      <c r="K49">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L49">
+        <v>1.526</v>
+      </c>
+      <c r="M49">
+        <v>0.7276460100000001</v>
+      </c>
+      <c r="N49">
+        <v>0.7983539900000002</v>
+      </c>
+      <c r="O49">
+        <v>0.1916049576</v>
+      </c>
+      <c r="P49">
+        <v>0.6067490324000001</v>
+      </c>
+      <c r="Q49">
+        <v>1.5307490324</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1297063996364331</v>
+      </c>
+      <c r="T49">
+        <v>1.43085306507009</v>
+      </c>
+      <c r="U49">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V49">
+        <v>0.24</v>
+      </c>
+      <c r="W49">
+        <v>0.056924</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.097173596815298</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.09554957711351159</v>
+      </c>
+      <c r="C50">
+        <v>9.650738250420615</v>
+      </c>
+      <c r="D50">
+        <v>14.79233825042061</v>
+      </c>
+      <c r="E50">
+        <v>0.5516000000000005</v>
+      </c>
+      <c r="F50">
+        <v>9.9216</v>
+      </c>
+      <c r="G50">
+        <v>4.78</v>
+      </c>
+      <c r="H50">
+        <v>11.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>2.45</v>
+      </c>
+      <c r="K50">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L50">
+        <v>1.526</v>
+      </c>
+      <c r="M50">
+        <v>0.7431278399999999</v>
+      </c>
+      <c r="N50">
+        <v>0.7828721600000004</v>
+      </c>
+      <c r="O50">
+        <v>0.1878893184000001</v>
+      </c>
+      <c r="P50">
+        <v>0.5949828416000003</v>
+      </c>
+      <c r="Q50">
+        <v>1.5189828416</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1312039559875223</v>
+      </c>
+      <c r="T50">
+        <v>1.45442437692097</v>
+      </c>
+      <c r="U50">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V50">
+        <v>0.24</v>
+      </c>
+      <c r="W50">
+        <v>0.056924</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>2.05348248021498</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.09560048241971361</v>
+      </c>
+      <c r="C51">
+        <v>9.430781170973338</v>
+      </c>
+      <c r="D51">
+        <v>14.77908117097334</v>
+      </c>
+      <c r="E51">
+        <v>0.758300000000002</v>
+      </c>
+      <c r="F51">
+        <v>10.1283</v>
+      </c>
+      <c r="G51">
+        <v>4.78</v>
+      </c>
+      <c r="H51">
+        <v>11.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>2.45</v>
+      </c>
+      <c r="K51">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L51">
+        <v>1.526</v>
+      </c>
+      <c r="M51">
+        <v>0.75860967</v>
+      </c>
+      <c r="N51">
+        <v>0.7673903300000002</v>
+      </c>
+      <c r="O51">
+        <v>0.1841736792000001</v>
+      </c>
+      <c r="P51">
+        <v>0.5832166508000002</v>
+      </c>
+      <c r="Q51">
+        <v>1.5072166508</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1327602400386542</v>
+      </c>
+      <c r="T51">
+        <v>1.478920053942474</v>
+      </c>
+      <c r="U51">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V51">
+        <v>0.24</v>
+      </c>
+      <c r="W51">
+        <v>0.056924</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>2.011574674496306</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1018453877259157</v>
+      </c>
+      <c r="C52">
+        <v>7.76015231345497</v>
+      </c>
+      <c r="D52">
+        <v>13.31515231345497</v>
+      </c>
+      <c r="E52">
+        <v>0.9650000000000016</v>
+      </c>
+      <c r="F52">
+        <v>10.335</v>
+      </c>
+      <c r="G52">
+        <v>4.78</v>
+      </c>
+      <c r="H52">
+        <v>11.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2.45</v>
+      </c>
+      <c r="K52">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L52">
+        <v>1.526</v>
+      </c>
+      <c r="M52">
+        <v>0.9425520000000001</v>
+      </c>
+      <c r="N52">
+        <v>0.5834480000000002</v>
+      </c>
+      <c r="O52">
+        <v>0.14002752</v>
+      </c>
+      <c r="P52">
+        <v>0.4434204800000001</v>
+      </c>
+      <c r="Q52">
+        <v>1.36742048</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1343787754518314</v>
+      </c>
+      <c r="T52">
+        <v>1.504395558044838</v>
+      </c>
+      <c r="U52">
+        <v>0.0912</v>
+      </c>
+      <c r="V52">
+        <v>0.24</v>
+      </c>
+      <c r="W52">
+        <v>0.069312</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>1.619008818611599</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1020201730321177</v>
+      </c>
+      <c r="C53">
+        <v>7.516639807847751</v>
+      </c>
+      <c r="D53">
+        <v>13.27833980784775</v>
+      </c>
+      <c r="E53">
+        <v>1.171700000000001</v>
+      </c>
+      <c r="F53">
+        <v>10.5417</v>
+      </c>
+      <c r="G53">
+        <v>4.78</v>
+      </c>
+      <c r="H53">
+        <v>11.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2.45</v>
+      </c>
+      <c r="K53">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L53">
+        <v>1.526</v>
+      </c>
+      <c r="M53">
+        <v>0.9614030400000001</v>
+      </c>
+      <c r="N53">
+        <v>0.5645969600000001</v>
+      </c>
+      <c r="O53">
+        <v>0.1355032704</v>
+      </c>
+      <c r="P53">
+        <v>0.4290936896000001</v>
+      </c>
+      <c r="Q53">
+        <v>1.3530936896</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1360633735349341</v>
+      </c>
+      <c r="T53">
+        <v>1.530910878641175</v>
+      </c>
+      <c r="U53">
+        <v>0.0912</v>
+      </c>
+      <c r="V53">
+        <v>0.24</v>
+      </c>
+      <c r="W53">
+        <v>0.069312</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>1.587263547658431</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1021949583383198</v>
+      </c>
+      <c r="C54">
+        <v>7.27333029267489</v>
+      </c>
+      <c r="D54">
+        <v>13.24173029267489</v>
+      </c>
+      <c r="E54">
+        <v>1.378400000000003</v>
+      </c>
+      <c r="F54">
+        <v>10.7484</v>
+      </c>
+      <c r="G54">
+        <v>4.78</v>
+      </c>
+      <c r="H54">
+        <v>11.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2.45</v>
+      </c>
+      <c r="K54">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L54">
+        <v>1.526</v>
+      </c>
+      <c r="M54">
+        <v>0.9802540800000002</v>
+      </c>
+      <c r="N54">
+        <v>0.54574592</v>
+      </c>
+      <c r="O54">
+        <v>0.1309790208</v>
+      </c>
+      <c r="P54">
+        <v>0.4147668992</v>
+      </c>
+      <c r="Q54">
+        <v>1.3387668992</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1378181632048329</v>
+      </c>
+      <c r="T54">
+        <v>1.55853100426236</v>
+      </c>
+      <c r="U54">
+        <v>0.0912</v>
+      </c>
+      <c r="V54">
+        <v>0.24</v>
+      </c>
+      <c r="W54">
+        <v>0.069312</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>1.556739248664999</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1023697436445218</v>
+      </c>
+      <c r="C55">
+        <v>7.030222093566959</v>
+      </c>
+      <c r="D55">
+        <v>13.20532209356696</v>
+      </c>
+      <c r="E55">
+        <v>1.585100000000002</v>
+      </c>
+      <c r="F55">
+        <v>10.9551</v>
+      </c>
+      <c r="G55">
+        <v>4.78</v>
+      </c>
+      <c r="H55">
+        <v>11.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2.45</v>
+      </c>
+      <c r="K55">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L55">
+        <v>1.526</v>
+      </c>
+      <c r="M55">
+        <v>0.9991051200000002</v>
+      </c>
+      <c r="N55">
+        <v>0.5268948800000001</v>
+      </c>
+      <c r="O55">
+        <v>0.1264547712</v>
+      </c>
+      <c r="P55">
+        <v>0.4004401088</v>
+      </c>
+      <c r="Q55">
+        <v>1.3244401088</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1396476247755783</v>
+      </c>
+      <c r="T55">
+        <v>1.587326454378064</v>
+      </c>
+      <c r="U55">
+        <v>0.0912</v>
+      </c>
+      <c r="V55">
+        <v>0.24</v>
+      </c>
+      <c r="W55">
+        <v>0.069312</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>1.527366810010943</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.132855249515704</v>
+      </c>
+      <c r="C56">
+        <v>2.543368393617735</v>
+      </c>
+      <c r="D56">
+        <v>8.925168393617737</v>
+      </c>
+      <c r="E56">
+        <v>1.791800000000002</v>
+      </c>
+      <c r="F56">
+        <v>11.1618</v>
+      </c>
+      <c r="G56">
+        <v>4.78</v>
+      </c>
+      <c r="H56">
+        <v>11.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>2.45</v>
+      </c>
+      <c r="K56">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L56">
+        <v>1.526</v>
+      </c>
+      <c r="M56">
+        <v>1.74793788</v>
+      </c>
+      <c r="N56">
+        <v>-0.2219378800000003</v>
+      </c>
+      <c r="O56">
+        <v>-0.05326509120000006</v>
+      </c>
+      <c r="P56">
+        <v>-0.1686727888000002</v>
+      </c>
+      <c r="Q56">
+        <v>0.7553272111999998</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1434993087534551</v>
+      </c>
+      <c r="T56">
+        <v>1.647951381198041</v>
+      </c>
+      <c r="U56">
+        <v>0.1566</v>
+      </c>
+      <c r="V56">
+        <v>0.2095268969169545</v>
+      </c>
+      <c r="W56">
+        <v>0.1237880879428049</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.873028737153977</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1340332495157041</v>
+      </c>
+      <c r="C57">
+        <v>2.226267368543523</v>
+      </c>
+      <c r="D57">
+        <v>8.814767368543526</v>
+      </c>
+      <c r="E57">
+        <v>1.998500000000003</v>
+      </c>
+      <c r="F57">
+        <v>11.3685</v>
+      </c>
+      <c r="G57">
+        <v>4.78</v>
+      </c>
+      <c r="H57">
+        <v>11.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>2.45</v>
+      </c>
+      <c r="K57">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L57">
+        <v>1.526</v>
+      </c>
+      <c r="M57">
+        <v>1.780307100000001</v>
+      </c>
+      <c r="N57">
+        <v>-0.2543071000000003</v>
+      </c>
+      <c r="O57">
+        <v>-0.06103370400000008</v>
+      </c>
+      <c r="P57">
+        <v>-0.1932733960000003</v>
+      </c>
+      <c r="Q57">
+        <v>0.7307266039999997</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1458259600590875</v>
+      </c>
+      <c r="T57">
+        <v>1.684572523002442</v>
+      </c>
+      <c r="U57">
+        <v>0.1566</v>
+      </c>
+      <c r="V57">
+        <v>0.2057173169730098</v>
+      </c>
+      <c r="W57">
+        <v>0.1243846681620267</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.857155487387541</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.135211249515704</v>
+      </c>
+      <c r="C58">
+        <v>1.911864211367323</v>
+      </c>
+      <c r="D58">
+        <v>8.707064211367324</v>
+      </c>
+      <c r="E58">
+        <v>2.205200000000003</v>
+      </c>
+      <c r="F58">
+        <v>11.5752</v>
+      </c>
+      <c r="G58">
+        <v>4.78</v>
+      </c>
+      <c r="H58">
+        <v>11.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2.45</v>
+      </c>
+      <c r="K58">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L58">
+        <v>1.526</v>
+      </c>
+      <c r="M58">
+        <v>1.812676320000001</v>
+      </c>
+      <c r="N58">
+        <v>-0.2866763200000004</v>
+      </c>
+      <c r="O58">
+        <v>-0.0688023168000001</v>
+      </c>
+      <c r="P58">
+        <v>-0.2178740032000003</v>
+      </c>
+      <c r="Q58">
+        <v>0.7061259967999995</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1482583682422485</v>
+      </c>
+      <c r="T58">
+        <v>1.722858262161588</v>
+      </c>
+      <c r="U58">
+        <v>0.1566</v>
+      </c>
+      <c r="V58">
+        <v>0.2020437934556346</v>
+      </c>
+      <c r="W58">
+        <v>0.1249599419448476</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.8418491393984777</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.136389249515704</v>
+      </c>
+      <c r="C59">
+        <v>1.600061224184904</v>
+      </c>
+      <c r="D59">
+        <v>8.601961224184906</v>
+      </c>
+      <c r="E59">
+        <v>2.411900000000003</v>
+      </c>
+      <c r="F59">
+        <v>11.7819</v>
+      </c>
+      <c r="G59">
+        <v>4.78</v>
+      </c>
+      <c r="H59">
+        <v>11.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2.45</v>
+      </c>
+      <c r="K59">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L59">
+        <v>1.526</v>
+      </c>
+      <c r="M59">
+        <v>1.845045540000001</v>
+      </c>
+      <c r="N59">
+        <v>-0.3190455400000003</v>
+      </c>
+      <c r="O59">
+        <v>-0.07657092960000007</v>
+      </c>
+      <c r="P59">
+        <v>-0.2424746104000002</v>
+      </c>
+      <c r="Q59">
+        <v>0.6815253895999998</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1508039116897427</v>
+      </c>
+      <c r="T59">
+        <v>1.762924733374648</v>
+      </c>
+      <c r="U59">
+        <v>0.1566</v>
+      </c>
+      <c r="V59">
+        <v>0.1984991655002727</v>
+      </c>
+      <c r="W59">
+        <v>0.1255150306826573</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.8270798562511361</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.137567249515704</v>
+      </c>
+      <c r="C60">
+        <v>1.29076537007561</v>
+      </c>
+      <c r="D60">
+        <v>8.499365370075608</v>
+      </c>
+      <c r="E60">
+        <v>2.618600000000001</v>
+      </c>
+      <c r="F60">
+        <v>11.9886</v>
+      </c>
+      <c r="G60">
+        <v>4.78</v>
+      </c>
+      <c r="H60">
+        <v>11.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2.45</v>
+      </c>
+      <c r="K60">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L60">
+        <v>1.526</v>
+      </c>
+      <c r="M60">
+        <v>1.87741476</v>
+      </c>
+      <c r="N60">
+        <v>-0.3514147599999999</v>
+      </c>
+      <c r="O60">
+        <v>-0.08433954239999998</v>
+      </c>
+      <c r="P60">
+        <v>-0.2670752176</v>
+      </c>
+      <c r="Q60">
+        <v>0.6569247824</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1534706714918794</v>
+      </c>
+      <c r="T60">
+        <v>1.80489913178833</v>
+      </c>
+      <c r="U60">
+        <v>0.1566</v>
+      </c>
+      <c r="V60">
+        <v>0.1950767660950956</v>
+      </c>
+      <c r="W60">
+        <v>0.126050978429508</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.812819858729565</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.17107935961301</v>
+      </c>
+      <c r="C61">
+        <v>-1.069193225010526</v>
+      </c>
+      <c r="D61">
+        <v>6.346106774989473</v>
+      </c>
+      <c r="E61">
+        <v>2.8253</v>
+      </c>
+      <c r="F61">
+        <v>12.1953</v>
+      </c>
+      <c r="G61">
+        <v>4.78</v>
+      </c>
+      <c r="H61">
+        <v>11.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>2.45</v>
+      </c>
+      <c r="K61">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L61">
+        <v>1.526</v>
+      </c>
+      <c r="M61">
+        <v>2.54637864</v>
+      </c>
+      <c r="N61">
+        <v>-1.02037864</v>
+      </c>
+      <c r="O61">
+        <v>-0.2448908735999999</v>
+      </c>
+      <c r="P61">
+        <v>-0.7754877663999997</v>
+      </c>
+      <c r="Q61">
+        <v>0.1485122336000002</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.160014127131452</v>
+      </c>
+      <c r="T61">
+        <v>1.907892139931624</v>
+      </c>
+      <c r="U61">
+        <v>0.2088</v>
+      </c>
+      <c r="V61">
+        <v>0.1438277851718078</v>
+      </c>
+      <c r="W61">
+        <v>0.1787687584561266</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5992824382158657</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.17277935961301</v>
+      </c>
+      <c r="C62">
+        <v>-1.356415937976493</v>
+      </c>
+      <c r="D62">
+        <v>6.265584062023509</v>
+      </c>
+      <c r="E62">
+        <v>3.032000000000002</v>
+      </c>
+      <c r="F62">
+        <v>12.402</v>
+      </c>
+      <c r="G62">
+        <v>4.78</v>
+      </c>
+      <c r="H62">
+        <v>11.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2.45</v>
+      </c>
+      <c r="K62">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L62">
+        <v>1.526</v>
+      </c>
+      <c r="M62">
+        <v>2.5895376</v>
+      </c>
+      <c r="N62">
+        <v>-1.0635376</v>
+      </c>
+      <c r="O62">
+        <v>-0.255249024</v>
+      </c>
+      <c r="P62">
+        <v>-0.808288576</v>
+      </c>
+      <c r="Q62">
+        <v>0.1157114239999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1630444803097383</v>
+      </c>
+      <c r="T62">
+        <v>1.955589443429914</v>
+      </c>
+      <c r="U62">
+        <v>0.2088</v>
+      </c>
+      <c r="V62">
+        <v>0.1414306554189443</v>
+      </c>
+      <c r="W62">
+        <v>0.1792692791485244</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5892943975789346</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.17447935961301</v>
+      </c>
+      <c r="C63">
+        <v>-1.641620825793037</v>
+      </c>
+      <c r="D63">
+        <v>6.187079174206963</v>
+      </c>
+      <c r="E63">
+        <v>3.238700000000001</v>
+      </c>
+      <c r="F63">
+        <v>12.6087</v>
+      </c>
+      <c r="G63">
+        <v>4.78</v>
+      </c>
+      <c r="H63">
+        <v>11.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2.45</v>
+      </c>
+      <c r="K63">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L63">
+        <v>1.526</v>
+      </c>
+      <c r="M63">
+        <v>2.63269656</v>
+      </c>
+      <c r="N63">
+        <v>-1.10669656</v>
+      </c>
+      <c r="O63">
+        <v>-0.2656071744</v>
+      </c>
+      <c r="P63">
+        <v>-0.8410893856000001</v>
+      </c>
+      <c r="Q63">
+        <v>0.0829106143999998</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1662302362151162</v>
+      </c>
+      <c r="T63">
+        <v>2.00573276249222</v>
+      </c>
+      <c r="U63">
+        <v>0.2088</v>
+      </c>
+      <c r="V63">
+        <v>0.1391121200842075</v>
+      </c>
+      <c r="W63">
+        <v>0.1797533893264175</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.579633833684198</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.17617935961301</v>
+      </c>
+      <c r="C64">
+        <v>-1.924882797153076</v>
+      </c>
+      <c r="D64">
+        <v>6.110517202846924</v>
+      </c>
+      <c r="E64">
+        <v>3.445400000000001</v>
+      </c>
+      <c r="F64">
+        <v>12.8154</v>
+      </c>
+      <c r="G64">
+        <v>4.78</v>
+      </c>
+      <c r="H64">
+        <v>11.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2.45</v>
+      </c>
+      <c r="K64">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L64">
+        <v>1.526</v>
+      </c>
+      <c r="M64">
+        <v>2.67585552</v>
+      </c>
+      <c r="N64">
+        <v>-1.14985552</v>
+      </c>
+      <c r="O64">
+        <v>-0.2759653248</v>
+      </c>
+      <c r="P64">
+        <v>-0.8738901952</v>
+      </c>
+      <c r="Q64">
+        <v>0.05010980479999994</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1695836634839351</v>
+      </c>
+      <c r="T64">
+        <v>2.058515203610436</v>
+      </c>
+      <c r="U64">
+        <v>0.2088</v>
+      </c>
+      <c r="V64">
+        <v>0.1368683762118816</v>
+      </c>
+      <c r="W64">
+        <v>0.1802218830469591</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5702849008828399</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.17787935961301</v>
+      </c>
+      <c r="C65">
+        <v>-2.206273098242644</v>
+      </c>
+      <c r="D65">
+        <v>6.035826901757359</v>
+      </c>
+      <c r="E65">
+        <v>3.652100000000003</v>
+      </c>
+      <c r="F65">
+        <v>13.0221</v>
+      </c>
+      <c r="G65">
+        <v>4.78</v>
+      </c>
+      <c r="H65">
+        <v>11.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2.45</v>
+      </c>
+      <c r="K65">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L65">
+        <v>1.526</v>
+      </c>
+      <c r="M65">
+        <v>2.719014480000001</v>
+      </c>
+      <c r="N65">
+        <v>-1.19301448</v>
+      </c>
+      <c r="O65">
+        <v>-0.2863234752000001</v>
+      </c>
+      <c r="P65">
+        <v>-0.9066910048000003</v>
+      </c>
+      <c r="Q65">
+        <v>0.01730899519999962</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.173118357091609</v>
+      </c>
+      <c r="T65">
+        <v>2.114150749653962</v>
+      </c>
+      <c r="U65">
+        <v>0.2088</v>
+      </c>
+      <c r="V65">
+        <v>0.1346958623037564</v>
+      </c>
+      <c r="W65">
+        <v>0.1806755039509757</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.5612327595989852</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.17957935961301</v>
+      </c>
+      <c r="C66">
+        <v>-2.485859533876345</v>
+      </c>
+      <c r="D66">
+        <v>5.962940466123657</v>
+      </c>
+      <c r="E66">
+        <v>3.858800000000002</v>
+      </c>
+      <c r="F66">
+        <v>13.2288</v>
+      </c>
+      <c r="G66">
+        <v>4.78</v>
+      </c>
+      <c r="H66">
+        <v>11.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2.45</v>
+      </c>
+      <c r="K66">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L66">
+        <v>1.526</v>
+      </c>
+      <c r="M66">
+        <v>2.762173440000001</v>
+      </c>
+      <c r="N66">
+        <v>-1.23617344</v>
+      </c>
+      <c r="O66">
+        <v>-0.2966816256000001</v>
+      </c>
+      <c r="P66">
+        <v>-0.9394918144000003</v>
+      </c>
+      <c r="Q66">
+        <v>-0.01549181440000036</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1768494225663759</v>
+      </c>
+      <c r="T66">
+        <v>2.172877159366571</v>
+      </c>
+      <c r="U66">
+        <v>0.2088</v>
+      </c>
+      <c r="V66">
+        <v>0.1325912394552602</v>
+      </c>
+      <c r="W66">
+        <v>0.1811149492017417</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5524634977302512</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.18127935961301</v>
+      </c>
+      <c r="C67">
+        <v>-2.763706672801895</v>
+      </c>
+      <c r="D67">
+        <v>5.891793327198106</v>
+      </c>
+      <c r="E67">
+        <v>4.065500000000002</v>
+      </c>
+      <c r="F67">
+        <v>13.4355</v>
+      </c>
+      <c r="G67">
+        <v>4.78</v>
+      </c>
+      <c r="H67">
+        <v>11.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2.45</v>
+      </c>
+      <c r="K67">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L67">
+        <v>1.526</v>
+      </c>
+      <c r="M67">
+        <v>2.805332400000001</v>
+      </c>
+      <c r="N67">
+        <v>-1.2793324</v>
+      </c>
+      <c r="O67">
+        <v>-0.3070397760000001</v>
+      </c>
+      <c r="P67">
+        <v>-0.9722926240000003</v>
+      </c>
+      <c r="Q67">
+        <v>-0.04829262400000034</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1807936917825581</v>
+      </c>
+      <c r="T67">
+        <v>2.234959363919902</v>
+      </c>
+      <c r="U67">
+        <v>0.2088</v>
+      </c>
+      <c r="V67">
+        <v>0.1305513742328717</v>
+      </c>
+      <c r="W67">
+        <v>0.1815408730601764</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5439640593036319</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.18297935961301</v>
+      </c>
+      <c r="C68">
+        <v>-3.039876038480315</v>
+      </c>
+      <c r="D68">
+        <v>5.822323961519686</v>
+      </c>
+      <c r="E68">
+        <v>4.272200000000003</v>
+      </c>
+      <c r="F68">
+        <v>13.6422</v>
+      </c>
+      <c r="G68">
+        <v>4.78</v>
+      </c>
+      <c r="H68">
+        <v>11.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2.45</v>
+      </c>
+      <c r="K68">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L68">
+        <v>1.526</v>
+      </c>
+      <c r="M68">
+        <v>2.848491360000001</v>
+      </c>
+      <c r="N68">
+        <v>-1.32249136</v>
+      </c>
+      <c r="O68">
+        <v>-0.3173979264000001</v>
+      </c>
+      <c r="P68">
+        <v>-1.0050934336</v>
+      </c>
+      <c r="Q68">
+        <v>-0.08109343360000043</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1849699768349863</v>
+      </c>
+      <c r="T68">
+        <v>2.300693462858723</v>
+      </c>
+      <c r="U68">
+        <v>0.2088</v>
+      </c>
+      <c r="V68">
+        <v>0.1285733231081312</v>
+      </c>
+      <c r="W68">
+        <v>0.1819538901350222</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5357221796172131</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.18467935961301</v>
+      </c>
+      <c r="C69">
+        <v>-3.314426286526654</v>
+      </c>
+      <c r="D69">
+        <v>5.754473713473348</v>
+      </c>
+      <c r="E69">
+        <v>4.478900000000003</v>
+      </c>
+      <c r="F69">
+        <v>13.8489</v>
+      </c>
+      <c r="G69">
+        <v>4.78</v>
+      </c>
+      <c r="H69">
+        <v>11.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2.45</v>
+      </c>
+      <c r="K69">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L69">
+        <v>1.526</v>
+      </c>
+      <c r="M69">
+        <v>2.891650320000001</v>
+      </c>
+      <c r="N69">
+        <v>-1.36565032</v>
+      </c>
+      <c r="O69">
+        <v>-0.3277560768000001</v>
+      </c>
+      <c r="P69">
+        <v>-1.0378942432</v>
+      </c>
+      <c r="Q69">
+        <v>-0.1138942432000003</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1893993700724101</v>
+      </c>
+      <c r="T69">
+        <v>2.370411446581715</v>
+      </c>
+      <c r="U69">
+        <v>0.2088</v>
+      </c>
+      <c r="V69">
+        <v>0.1266543182856217</v>
+      </c>
+      <c r="W69">
+        <v>0.1823545783419622</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5277263261900906</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.18637935961301</v>
+      </c>
+      <c r="C70">
+        <v>-3.5874133698868</v>
+      </c>
+      <c r="D70">
+        <v>5.688186630113202</v>
+      </c>
+      <c r="E70">
+        <v>4.685600000000003</v>
+      </c>
+      <c r="F70">
+        <v>14.0556</v>
+      </c>
+      <c r="G70">
+        <v>4.78</v>
+      </c>
+      <c r="H70">
+        <v>11.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2.45</v>
+      </c>
+      <c r="K70">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L70">
+        <v>1.526</v>
+      </c>
+      <c r="M70">
+        <v>2.934809280000001</v>
+      </c>
+      <c r="N70">
+        <v>-1.40880928</v>
+      </c>
+      <c r="O70">
+        <v>-0.3381142272000001</v>
+      </c>
+      <c r="P70">
+        <v>-1.0706950528</v>
+      </c>
+      <c r="Q70">
+        <v>-0.1466950528000002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1941056003871729</v>
+      </c>
+      <c r="T70">
+        <v>2.444486804287393</v>
+      </c>
+      <c r="U70">
+        <v>0.2088</v>
+      </c>
+      <c r="V70">
+        <v>0.1247917547814214</v>
+      </c>
+      <c r="W70">
+        <v>0.1827434816016392</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5199656449225893</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.18807935961301</v>
+      </c>
+      <c r="C71">
+        <v>-3.858890692728087</v>
+      </c>
+      <c r="D71">
+        <v>5.623409307271913</v>
+      </c>
+      <c r="E71">
+        <v>4.892300000000002</v>
+      </c>
+      <c r="F71">
+        <v>14.2623</v>
+      </c>
+      <c r="G71">
+        <v>4.78</v>
+      </c>
+      <c r="H71">
+        <v>11.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2.45</v>
+      </c>
+      <c r="K71">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L71">
+        <v>1.526</v>
+      </c>
+      <c r="M71">
+        <v>2.97796824</v>
+      </c>
+      <c r="N71">
+        <v>-1.45196824</v>
+      </c>
+      <c r="O71">
+        <v>-0.3484723776</v>
+      </c>
+      <c r="P71">
+        <v>-1.1034958624</v>
+      </c>
+      <c r="Q71">
+        <v>-0.1794958624000003</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1991154584641785</v>
+      </c>
+      <c r="T71">
+        <v>2.523341217328922</v>
+      </c>
+      <c r="U71">
+        <v>0.2088</v>
+      </c>
+      <c r="V71">
+        <v>0.122983178625169</v>
+      </c>
+      <c r="W71">
+        <v>0.1831211123030647</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.512429910938204</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.18977935961301</v>
+      </c>
+      <c r="C72">
+        <v>-4.128909253933182</v>
+      </c>
+      <c r="D72">
+        <v>5.560090746066821</v>
+      </c>
+      <c r="E72">
+        <v>5.099000000000004</v>
+      </c>
+      <c r="F72">
+        <v>14.469</v>
+      </c>
+      <c r="G72">
+        <v>4.78</v>
+      </c>
+      <c r="H72">
+        <v>11.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2.45</v>
+      </c>
+      <c r="K72">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L72">
+        <v>1.526</v>
+      </c>
+      <c r="M72">
+        <v>3.021127200000001</v>
+      </c>
+      <c r="N72">
+        <v>-1.495127200000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.3588305280000001</v>
+      </c>
+      <c r="P72">
+        <v>-1.136296672000001</v>
+      </c>
+      <c r="Q72">
+        <v>-0.2122966720000006</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2044593070796511</v>
+      </c>
+      <c r="T72">
+        <v>2.607452591239886</v>
+      </c>
+      <c r="U72">
+        <v>0.2088</v>
+      </c>
+      <c r="V72">
+        <v>0.1212262760733808</v>
+      </c>
+      <c r="W72">
+        <v>0.1834879535558781</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.5051094836390867</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2133582955793314</v>
+      </c>
+      <c r="C73">
+        <v>-5.086653615550839</v>
+      </c>
+      <c r="D73">
+        <v>4.809046384449162</v>
+      </c>
+      <c r="E73">
+        <v>5.305700000000002</v>
+      </c>
+      <c r="F73">
+        <v>14.6757</v>
+      </c>
+      <c r="G73">
+        <v>4.78</v>
+      </c>
+      <c r="H73">
+        <v>11.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2.45</v>
+      </c>
+      <c r="K73">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L73">
+        <v>1.526</v>
+      </c>
+      <c r="M73">
+        <v>3.504557160000001</v>
+      </c>
+      <c r="N73">
+        <v>-1.97855716</v>
+      </c>
+      <c r="O73">
+        <v>-0.4748537184000001</v>
+      </c>
+      <c r="P73">
+        <v>-1.5037034416</v>
+      </c>
+      <c r="Q73">
+        <v>-0.5797034416000002</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2121680278972989</v>
+      </c>
+      <c r="T73">
+        <v>2.728786698121404</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.1045039311043795</v>
+      </c>
+      <c r="W73">
+        <v>0.2138444612522742</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.4354330462682481</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2153582955793313</v>
+      </c>
+      <c r="C74">
+        <v>-5.347829066490929</v>
+      </c>
+      <c r="D74">
+        <v>4.754570933509071</v>
+      </c>
+      <c r="E74">
+        <v>5.512400000000001</v>
+      </c>
+      <c r="F74">
+        <v>14.8824</v>
+      </c>
+      <c r="G74">
+        <v>4.78</v>
+      </c>
+      <c r="H74">
+        <v>11.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2.45</v>
+      </c>
+      <c r="K74">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L74">
+        <v>1.526</v>
+      </c>
+      <c r="M74">
+        <v>3.55391712</v>
+      </c>
+      <c r="N74">
+        <v>-2.02791712</v>
+      </c>
+      <c r="O74">
+        <v>-0.4867001088</v>
+      </c>
+      <c r="P74">
+        <v>-1.5412170112</v>
+      </c>
+      <c r="Q74">
+        <v>-0.6172170112000002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2183597431793453</v>
+      </c>
+      <c r="T74">
+        <v>2.826243365911453</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.1030524876168187</v>
+      </c>
+      <c r="W74">
+        <v>0.2141910659571037</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.429385365070078</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2173582955793313</v>
+      </c>
+      <c r="C75">
+        <v>-5.607784177580369</v>
+      </c>
+      <c r="D75">
+        <v>4.701315822419631</v>
+      </c>
+      <c r="E75">
+        <v>5.719100000000001</v>
+      </c>
+      <c r="F75">
+        <v>15.0891</v>
+      </c>
+      <c r="G75">
+        <v>4.78</v>
+      </c>
+      <c r="H75">
+        <v>11.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2.45</v>
+      </c>
+      <c r="K75">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L75">
+        <v>1.526</v>
+      </c>
+      <c r="M75">
+        <v>3.60327708</v>
+      </c>
+      <c r="N75">
+        <v>-2.07727708</v>
+      </c>
+      <c r="O75">
+        <v>-0.4985464992</v>
+      </c>
+      <c r="P75">
+        <v>-1.5787305808</v>
+      </c>
+      <c r="Q75">
+        <v>-0.6547305808000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2250101040378395</v>
+      </c>
+      <c r="T75">
+        <v>2.930919046130396</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.1016408097042596</v>
+      </c>
+      <c r="W75">
+        <v>0.2145281746426228</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.4235033737677482</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2193582955793313</v>
+      </c>
+      <c r="C76">
+        <v>-5.866559501035715</v>
+      </c>
+      <c r="D76">
+        <v>4.649240498964287</v>
+      </c>
+      <c r="E76">
+        <v>5.925800000000002</v>
+      </c>
+      <c r="F76">
+        <v>15.2958</v>
+      </c>
+      <c r="G76">
+        <v>4.78</v>
+      </c>
+      <c r="H76">
+        <v>11.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2.45</v>
+      </c>
+      <c r="K76">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L76">
+        <v>1.526</v>
+      </c>
+      <c r="M76">
+        <v>3.652637040000001</v>
+      </c>
+      <c r="N76">
+        <v>-2.12663704</v>
+      </c>
+      <c r="O76">
+        <v>-0.5103928896000001</v>
+      </c>
+      <c r="P76">
+        <v>-1.6162441504</v>
+      </c>
+      <c r="Q76">
+        <v>-0.6922441504000003</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.232172031116218</v>
+      </c>
+      <c r="T76">
+        <v>3.043646701750796</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.1002672852487966</v>
+      </c>
+      <c r="W76">
+        <v>0.2148561722825874</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.4177803552033191</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2213582955793313</v>
+      </c>
+      <c r="C77">
+        <v>-6.124193812009754</v>
+      </c>
+      <c r="D77">
+        <v>4.598306187990247</v>
+      </c>
+      <c r="E77">
+        <v>6.132500000000002</v>
+      </c>
+      <c r="F77">
+        <v>15.5025</v>
+      </c>
+      <c r="G77">
+        <v>4.78</v>
+      </c>
+      <c r="H77">
+        <v>11.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2.45</v>
+      </c>
+      <c r="K77">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L77">
+        <v>1.526</v>
+      </c>
+      <c r="M77">
+        <v>3.701997</v>
+      </c>
+      <c r="N77">
+        <v>-2.175997</v>
+      </c>
+      <c r="O77">
+        <v>-0.52223928</v>
+      </c>
+      <c r="P77">
+        <v>-1.65375772</v>
+      </c>
+      <c r="Q77">
+        <v>-0.7297577200000003</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2399069123608667</v>
+      </c>
+      <c r="T77">
+        <v>3.165392569820829</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.09893038811214595</v>
+      </c>
+      <c r="W77">
+        <v>0.2151754233188196</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.4122099504672748</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2233582955793313</v>
+      </c>
+      <c r="C78">
+        <v>-6.380724204878913</v>
+      </c>
+      <c r="D78">
+        <v>4.548475795121088</v>
+      </c>
+      <c r="E78">
+        <v>6.339200000000002</v>
+      </c>
+      <c r="F78">
+        <v>15.7092</v>
+      </c>
+      <c r="G78">
+        <v>4.78</v>
+      </c>
+      <c r="H78">
+        <v>11.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2.45</v>
+      </c>
+      <c r="K78">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L78">
+        <v>1.526</v>
+      </c>
+      <c r="M78">
+        <v>3.75135696</v>
+      </c>
+      <c r="N78">
+        <v>-2.22535696</v>
+      </c>
+      <c r="O78">
+        <v>-0.5340856704</v>
+      </c>
+      <c r="P78">
+        <v>-1.6912712896</v>
+      </c>
+      <c r="Q78">
+        <v>-0.7672712896</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2482863670425695</v>
+      </c>
+      <c r="T78">
+        <v>3.297283926896696</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.09762867247909141</v>
+      </c>
+      <c r="W78">
+        <v>0.215486273011993</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.4067861353295475</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2253582955793313</v>
+      </c>
+      <c r="C79">
+        <v>-6.636186183337136</v>
+      </c>
+      <c r="D79">
+        <v>4.499713816662865</v>
+      </c>
+      <c r="E79">
+        <v>6.545900000000003</v>
+      </c>
+      <c r="F79">
+        <v>15.9159</v>
+      </c>
+      <c r="G79">
+        <v>4.78</v>
+      </c>
+      <c r="H79">
+        <v>11.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2.45</v>
+      </c>
+      <c r="K79">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L79">
+        <v>1.526</v>
+      </c>
+      <c r="M79">
+        <v>3.800716920000001</v>
+      </c>
+      <c r="N79">
+        <v>-2.27471692</v>
+      </c>
+      <c r="O79">
+        <v>-0.5459320608000001</v>
+      </c>
+      <c r="P79">
+        <v>-1.7287848592</v>
+      </c>
+      <c r="Q79">
+        <v>-0.8047848592000002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2573944699574638</v>
+      </c>
+      <c r="T79">
+        <v>3.440644097631335</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.09636076764170061</v>
+      </c>
+      <c r="W79">
+        <v>0.2157890486871619</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.4015031985070858</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2273582955793314</v>
+      </c>
+      <c r="C80">
+        <v>-6.890613744756147</v>
+      </c>
+      <c r="D80">
+        <v>4.451986255243855</v>
+      </c>
+      <c r="E80">
+        <v>6.752600000000003</v>
+      </c>
+      <c r="F80">
+        <v>16.1226</v>
+      </c>
+      <c r="G80">
+        <v>4.78</v>
+      </c>
+      <c r="H80">
+        <v>11.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2.45</v>
+      </c>
+      <c r="K80">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L80">
+        <v>1.526</v>
+      </c>
+      <c r="M80">
+        <v>3.85007688</v>
+      </c>
+      <c r="N80">
+        <v>-2.32407688</v>
+      </c>
+      <c r="O80">
+        <v>-0.5577784512</v>
+      </c>
+      <c r="P80">
+        <v>-1.7662984288</v>
+      </c>
+      <c r="Q80">
+        <v>-0.8422984288000004</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2673305822282576</v>
+      </c>
+      <c r="T80">
+        <v>3.597037011160032</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.09512537318475572</v>
+      </c>
+      <c r="W80">
+        <v>0.2160840608834804</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3963557216031489</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2293582955793314</v>
+      </c>
+      <c r="C81">
+        <v>-7.144039459233271</v>
+      </c>
+      <c r="D81">
+        <v>4.405260540766732</v>
+      </c>
+      <c r="E81">
+        <v>6.959300000000004</v>
+      </c>
+      <c r="F81">
+        <v>16.3293</v>
+      </c>
+      <c r="G81">
+        <v>4.78</v>
+      </c>
+      <c r="H81">
+        <v>11.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2.45</v>
+      </c>
+      <c r="K81">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L81">
+        <v>1.526</v>
+      </c>
+      <c r="M81">
+        <v>3.899436840000001</v>
+      </c>
+      <c r="N81">
+        <v>-2.373436840000001</v>
+      </c>
+      <c r="O81">
+        <v>-0.5696248416000003</v>
+      </c>
+      <c r="P81">
+        <v>-1.803811998400001</v>
+      </c>
+      <c r="Q81">
+        <v>-0.8798119984000008</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2782129909057938</v>
+      </c>
+      <c r="T81">
+        <v>3.768324487881939</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.09392125453684741</v>
+      </c>
+      <c r="W81">
+        <v>0.2163716044166009</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3913385605701976</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2313582955793314</v>
+      </c>
+      <c r="C82">
+        <v>-7.396494543713146</v>
+      </c>
+      <c r="D82">
+        <v>4.359505456286855</v>
+      </c>
+      <c r="E82">
+        <v>7.166000000000002</v>
+      </c>
+      <c r="F82">
+        <v>16.536</v>
+      </c>
+      <c r="G82">
+        <v>4.78</v>
+      </c>
+      <c r="H82">
+        <v>11.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2.45</v>
+      </c>
+      <c r="K82">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L82">
+        <v>1.526</v>
+      </c>
+      <c r="M82">
+        <v>3.948796800000001</v>
+      </c>
+      <c r="N82">
+        <v>-2.4227968</v>
+      </c>
+      <c r="O82">
+        <v>-0.5814712320000001</v>
+      </c>
+      <c r="P82">
+        <v>-1.841325568</v>
+      </c>
+      <c r="Q82">
+        <v>-0.9173255680000003</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2901836404510834</v>
+      </c>
+      <c r="T82">
+        <v>3.956740712276036</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.09274723885513683</v>
+      </c>
+      <c r="W82">
+        <v>0.2166519593613933</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3864468285630701</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2333582955793314</v>
+      </c>
+      <c r="C83">
+        <v>-7.648008931537689</v>
+      </c>
+      <c r="D83">
+        <v>4.314691068462314</v>
+      </c>
+      <c r="E83">
+        <v>7.372700000000004</v>
+      </c>
+      <c r="F83">
+        <v>16.7427</v>
+      </c>
+      <c r="G83">
+        <v>4.78</v>
+      </c>
+      <c r="H83">
+        <v>11.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2.45</v>
+      </c>
+      <c r="K83">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L83">
+        <v>1.526</v>
+      </c>
+      <c r="M83">
+        <v>3.998156760000001</v>
+      </c>
+      <c r="N83">
+        <v>-2.472156760000001</v>
+      </c>
+      <c r="O83">
+        <v>-0.5933176224000002</v>
+      </c>
+      <c r="P83">
+        <v>-1.8788391376</v>
+      </c>
+      <c r="Q83">
+        <v>-0.9548391376000005</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3034143583695615</v>
+      </c>
+      <c r="T83">
+        <v>4.164990223448458</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.09160221121494995</v>
+      </c>
+      <c r="W83">
+        <v>0.21692539196187</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3816758800622915</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2353582955793314</v>
+      </c>
+      <c r="C84">
+        <v>-7.898611337750008</v>
+      </c>
+      <c r="D84">
+        <v>4.270788662249997</v>
+      </c>
+      <c r="E84">
+        <v>7.579400000000005</v>
+      </c>
+      <c r="F84">
+        <v>16.9494</v>
+      </c>
+      <c r="G84">
+        <v>4.78</v>
+      </c>
+      <c r="H84">
+        <v>11.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2.45</v>
+      </c>
+      <c r="K84">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L84">
+        <v>1.526</v>
+      </c>
+      <c r="M84">
+        <v>4.047516720000001</v>
+      </c>
+      <c r="N84">
+        <v>-2.521516720000001</v>
+      </c>
+      <c r="O84">
+        <v>-0.6051640128000001</v>
+      </c>
+      <c r="P84">
+        <v>-1.916352707200001</v>
+      </c>
+      <c r="Q84">
+        <v>-0.9923527072000007</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3181151560567594</v>
+      </c>
+      <c r="T84">
+        <v>4.396378569195596</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.09048511107818227</v>
+      </c>
+      <c r="W84">
+        <v>0.2171921554745301</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3770212961590929</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2373582955793314</v>
+      </c>
+      <c r="C85">
+        <v>-8.148329320451653</v>
+      </c>
+      <c r="D85">
+        <v>4.227770679548349</v>
+      </c>
+      <c r="E85">
+        <v>7.786100000000003</v>
+      </c>
+      <c r="F85">
+        <v>17.1561</v>
+      </c>
+      <c r="G85">
+        <v>4.78</v>
+      </c>
+      <c r="H85">
+        <v>11.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2.45</v>
+      </c>
+      <c r="K85">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L85">
+        <v>1.526</v>
+      </c>
+      <c r="M85">
+        <v>4.096876680000001</v>
+      </c>
+      <c r="N85">
+        <v>-2.570876680000001</v>
+      </c>
+      <c r="O85">
+        <v>-0.6170104032000002</v>
+      </c>
+      <c r="P85">
+        <v>-1.953866276800001</v>
+      </c>
+      <c r="Q85">
+        <v>-1.029866276800001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3345454593542159</v>
+      </c>
+      <c r="T85">
+        <v>4.654989073265925</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.08939492901699934</v>
+      </c>
+      <c r="W85">
+        <v>0.2174524909507406</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.372478870904164</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2393582955793313</v>
+      </c>
+      <c r="C86">
+        <v>-8.397189338488662</v>
+      </c>
+      <c r="D86">
+        <v>4.185610661511339</v>
+      </c>
+      <c r="E86">
+        <v>7.992800000000001</v>
+      </c>
+      <c r="F86">
+        <v>17.3628</v>
+      </c>
+      <c r="G86">
+        <v>4.78</v>
+      </c>
+      <c r="H86">
+        <v>11.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2.45</v>
+      </c>
+      <c r="K86">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L86">
+        <v>1.526</v>
+      </c>
+      <c r="M86">
+        <v>4.146236640000001</v>
+      </c>
+      <c r="N86">
+        <v>-2.62023664</v>
+      </c>
+      <c r="O86">
+        <v>-0.6288567936</v>
+      </c>
+      <c r="P86">
+        <v>-1.9913798464</v>
+      </c>
+      <c r="Q86">
+        <v>-1.0673798464</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3530295505638542</v>
+      </c>
+      <c r="T86">
+        <v>4.945925890345043</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0883307036715589</v>
+      </c>
+      <c r="W86">
+        <v>0.2177066279632317</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3680445986314954</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2413582955793314</v>
+      </c>
+      <c r="C87">
+        <v>-8.645216805720157</v>
+      </c>
+      <c r="D87">
+        <v>4.144283194279843</v>
+      </c>
+      <c r="E87">
+        <v>8.199500000000002</v>
+      </c>
+      <c r="F87">
+        <v>17.5695</v>
+      </c>
+      <c r="G87">
+        <v>4.78</v>
+      </c>
+      <c r="H87">
+        <v>11.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2.45</v>
+      </c>
+      <c r="K87">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L87">
+        <v>1.526</v>
+      </c>
+      <c r="M87">
+        <v>4.195596600000001</v>
+      </c>
+      <c r="N87">
+        <v>-2.669596600000001</v>
+      </c>
+      <c r="O87">
+        <v>-0.6407031840000001</v>
+      </c>
+      <c r="P87">
+        <v>-2.028893416000001</v>
+      </c>
+      <c r="Q87">
+        <v>-1.104893416000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3739781872681112</v>
+      </c>
+      <c r="T87">
+        <v>5.275654283034714</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.08729151892248171</v>
+      </c>
+      <c r="W87">
+        <v>0.2179547852813114</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3637146621770072</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2433582955793314</v>
+      </c>
+      <c r="C88">
+        <v>-8.892436142103392</v>
+      </c>
+      <c r="D88">
+        <v>4.10376385789661</v>
+      </c>
+      <c r="E88">
+        <v>8.406200000000004</v>
+      </c>
+      <c r="F88">
+        <v>17.7762</v>
+      </c>
+      <c r="G88">
+        <v>4.78</v>
+      </c>
+      <c r="H88">
+        <v>11.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2.45</v>
+      </c>
+      <c r="K88">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L88">
+        <v>1.526</v>
+      </c>
+      <c r="M88">
+        <v>4.244956560000001</v>
+      </c>
+      <c r="N88">
+        <v>-2.718956560000001</v>
+      </c>
+      <c r="O88">
+        <v>-0.6525495744000002</v>
+      </c>
+      <c r="P88">
+        <v>-2.066406985600001</v>
+      </c>
+      <c r="Q88">
+        <v>-1.142406985600001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3979194863586906</v>
+      </c>
+      <c r="T88">
+        <v>5.652486731822908</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.08627650126059239</v>
+      </c>
+      <c r="W88">
+        <v>0.2181971714989706</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.359485421919135</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2453582955793313</v>
+      </c>
+      <c r="C89">
+        <v>-9.138870821810997</v>
+      </c>
+      <c r="D89">
+        <v>4.064029178189005</v>
+      </c>
+      <c r="E89">
+        <v>8.612900000000002</v>
+      </c>
+      <c r="F89">
+        <v>17.9829</v>
+      </c>
+      <c r="G89">
+        <v>4.78</v>
+      </c>
+      <c r="H89">
+        <v>11.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2.45</v>
+      </c>
+      <c r="K89">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L89">
+        <v>1.526</v>
+      </c>
+      <c r="M89">
+        <v>4.294316520000001</v>
+      </c>
+      <c r="N89">
+        <v>-2.76831652</v>
+      </c>
+      <c r="O89">
+        <v>-0.6643959648000001</v>
+      </c>
+      <c r="P89">
+        <v>-2.1039205552</v>
+      </c>
+      <c r="Q89">
+        <v>-1.1799205552</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.425544062232436</v>
+      </c>
+      <c r="T89">
+        <v>6.087293403501592</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.08528481733805686</v>
+      </c>
+      <c r="W89">
+        <v>0.218433985619672</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3553534055752369</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2473582955793314</v>
+      </c>
+      <c r="C90">
+        <v>-9.384543418579684</v>
+      </c>
+      <c r="D90">
+        <v>4.025056581420318</v>
+      </c>
+      <c r="E90">
+        <v>8.819600000000003</v>
+      </c>
+      <c r="F90">
+        <v>18.1896</v>
+      </c>
+      <c r="G90">
+        <v>4.78</v>
+      </c>
+      <c r="H90">
+        <v>11.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2.45</v>
+      </c>
+      <c r="K90">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L90">
+        <v>1.526</v>
+      </c>
+      <c r="M90">
+        <v>4.343676480000001</v>
+      </c>
+      <c r="N90">
+        <v>-2.817676480000001</v>
+      </c>
+      <c r="O90">
+        <v>-0.6762423552000001</v>
+      </c>
+      <c r="P90">
+        <v>-2.141434124800001</v>
+      </c>
+      <c r="Q90">
+        <v>-1.217434124800001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.457772734085139</v>
+      </c>
+      <c r="T90">
+        <v>6.594567853793393</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.08431567168648801</v>
+      </c>
+      <c r="W90">
+        <v>0.2186654176012667</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3513152986937002</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2493582955793313</v>
+      </c>
+      <c r="C91">
+        <v>-9.629475648474454</v>
+      </c>
+      <c r="D91">
+        <v>3.986824351525545</v>
+      </c>
+      <c r="E91">
+        <v>9.026300000000001</v>
+      </c>
+      <c r="F91">
+        <v>18.3963</v>
+      </c>
+      <c r="G91">
+        <v>4.78</v>
+      </c>
+      <c r="H91">
+        <v>11.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>2.45</v>
+      </c>
+      <c r="K91">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L91">
+        <v>1.526</v>
+      </c>
+      <c r="M91">
+        <v>4.39303644</v>
+      </c>
+      <c r="N91">
+        <v>-2.86703644</v>
+      </c>
+      <c r="O91">
+        <v>-0.6880887456</v>
+      </c>
+      <c r="P91">
+        <v>-2.1789476944</v>
+      </c>
+      <c r="Q91">
+        <v>-1.2549476944</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4958611644565152</v>
+      </c>
+      <c r="T91">
+        <v>7.194074022320064</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.08336830458888704</v>
+      </c>
+      <c r="W91">
+        <v>0.2188916488641738</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3473679357870294</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2513582955793313</v>
+      </c>
+      <c r="C92">
+        <v>-9.873688410238557</v>
+      </c>
+      <c r="D92">
+        <v>3.949311589761444</v>
+      </c>
+      <c r="E92">
+        <v>9.233000000000002</v>
+      </c>
+      <c r="F92">
+        <v>18.603</v>
+      </c>
+      <c r="G92">
+        <v>4.78</v>
+      </c>
+      <c r="H92">
+        <v>11.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>2.45</v>
+      </c>
+      <c r="K92">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L92">
+        <v>1.526</v>
+      </c>
+      <c r="M92">
+        <v>4.442396400000001</v>
+      </c>
+      <c r="N92">
+        <v>-2.9163964</v>
+      </c>
+      <c r="O92">
+        <v>-0.6999351360000001</v>
+      </c>
+      <c r="P92">
+        <v>-2.216461264</v>
+      </c>
+      <c r="Q92">
+        <v>-1.292461264</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5415672809021668</v>
+      </c>
+      <c r="T92">
+        <v>7.913481424552072</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.08244199009345497</v>
+      </c>
+      <c r="W92">
+        <v>0.219112852765683</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3435082920560624</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2533582955793313</v>
+      </c>
+      <c r="C93">
+        <v>-10.1172018233867</v>
+      </c>
+      <c r="D93">
+        <v>3.912498176613302</v>
+      </c>
+      <c r="E93">
+        <v>9.439700000000004</v>
+      </c>
+      <c r="F93">
+        <v>18.8097</v>
+      </c>
+      <c r="G93">
+        <v>4.78</v>
+      </c>
+      <c r="H93">
+        <v>11.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2.45</v>
+      </c>
+      <c r="K93">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L93">
+        <v>1.526</v>
+      </c>
+      <c r="M93">
+        <v>4.491756360000001</v>
+      </c>
+      <c r="N93">
+        <v>-2.965756360000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.7117815264000001</v>
+      </c>
+      <c r="P93">
+        <v>-2.253974833600001</v>
+      </c>
+      <c r="Q93">
+        <v>-1.329974833600001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5974303121135187</v>
+      </c>
+      <c r="T93">
+        <v>8.792757138391192</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.08153603415836204</v>
+      </c>
+      <c r="W93">
+        <v>0.2193291950429831</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3397334756598419</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2553582955793314</v>
+      </c>
+      <c r="C94">
+        <v>-10.36003526418745</v>
+      </c>
+      <c r="D94">
+        <v>3.876364735812554</v>
+      </c>
+      <c r="E94">
+        <v>9.646400000000002</v>
+      </c>
+      <c r="F94">
+        <v>19.0164</v>
+      </c>
+      <c r="G94">
+        <v>4.78</v>
+      </c>
+      <c r="H94">
+        <v>11.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2.45</v>
+      </c>
+      <c r="K94">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L94">
+        <v>1.526</v>
+      </c>
+      <c r="M94">
+        <v>4.54111632</v>
+      </c>
+      <c r="N94">
+        <v>-3.01511632</v>
+      </c>
+      <c r="O94">
+        <v>-0.7236279168</v>
+      </c>
+      <c r="P94">
+        <v>-2.2914884032</v>
+      </c>
+      <c r="Q94">
+        <v>-1.3674884032</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6672591011277087</v>
+      </c>
+      <c r="T94">
+        <v>9.891851780690093</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.0806497729175103</v>
+      </c>
+      <c r="W94">
+        <v>0.2195408342272986</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3360407204896262</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2573582955793314</v>
+      </c>
+      <c r="C95">
+        <v>-10.60220739967</v>
+      </c>
+      <c r="D95">
+        <v>3.840892600330005</v>
+      </c>
+      <c r="E95">
+        <v>9.853100000000003</v>
+      </c>
+      <c r="F95">
+        <v>19.2231</v>
+      </c>
+      <c r="G95">
+        <v>4.78</v>
+      </c>
+      <c r="H95">
+        <v>11.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>2.45</v>
+      </c>
+      <c r="K95">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L95">
+        <v>1.526</v>
+      </c>
+      <c r="M95">
+        <v>4.590476280000001</v>
+      </c>
+      <c r="N95">
+        <v>-3.06447628</v>
+      </c>
+      <c r="O95">
+        <v>-0.7354743072000001</v>
+      </c>
+      <c r="P95">
+        <v>-2.3290019728</v>
+      </c>
+      <c r="Q95">
+        <v>-1.4050019728</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7570389727173816</v>
+      </c>
+      <c r="T95">
+        <v>11.30497346364582</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.07978257105818222</v>
+      </c>
+      <c r="W95">
+        <v>0.2197479220313061</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3324273794090926</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2593582955793314</v>
+      </c>
+      <c r="C96">
+        <v>-10.84373621978072</v>
+      </c>
+      <c r="D96">
+        <v>3.806063780219283</v>
+      </c>
+      <c r="E96">
+        <v>10.0598</v>
+      </c>
+      <c r="F96">
+        <v>19.4298</v>
+      </c>
+      <c r="G96">
+        <v>4.78</v>
+      </c>
+      <c r="H96">
+        <v>11.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2.45</v>
+      </c>
+      <c r="K96">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L96">
+        <v>1.526</v>
+      </c>
+      <c r="M96">
+        <v>4.639836240000001</v>
+      </c>
+      <c r="N96">
+        <v>-3.113836240000001</v>
+      </c>
+      <c r="O96">
+        <v>-0.7473206976000002</v>
+      </c>
+      <c r="P96">
+        <v>-2.366515542400001</v>
+      </c>
+      <c r="Q96">
+        <v>-1.442515542400001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.8767454681702789</v>
+      </c>
+      <c r="T96">
+        <v>13.1891357075868</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.07893382030224411</v>
+      </c>
+      <c r="W96">
+        <v>0.2199506037118241</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3288909179260171</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2613582955793314</v>
+      </c>
+      <c r="C97">
+        <v>-11.08463906780588</v>
+      </c>
+      <c r="D97">
+        <v>3.771860932194123</v>
+      </c>
+      <c r="E97">
+        <v>10.2665</v>
+      </c>
+      <c r="F97">
+        <v>19.6365</v>
+      </c>
+      <c r="G97">
+        <v>4.78</v>
+      </c>
+      <c r="H97">
+        <v>11.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>2.45</v>
+      </c>
+      <c r="K97">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L97">
+        <v>1.526</v>
+      </c>
+      <c r="M97">
+        <v>4.6891962</v>
+      </c>
+      <c r="N97">
+        <v>-3.1631962</v>
+      </c>
+      <c r="O97">
+        <v>-0.759167088</v>
+      </c>
+      <c r="P97">
+        <v>-2.404029112</v>
+      </c>
+      <c r="Q97">
+        <v>-1.480029112</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.044334561804335</v>
+      </c>
+      <c r="T97">
+        <v>15.82696284910416</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.07810293798327313</v>
+      </c>
+      <c r="W97">
+        <v>0.2201490184095944</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.325428908263638</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2633582955793313</v>
+      </c>
+      <c r="C98">
+        <v>-11.32493266916862</v>
+      </c>
+      <c r="D98">
+        <v>3.738267330831384</v>
+      </c>
+      <c r="E98">
+        <v>10.4732</v>
+      </c>
+      <c r="F98">
+        <v>19.8432</v>
+      </c>
+      <c r="G98">
+        <v>4.78</v>
+      </c>
+      <c r="H98">
+        <v>11.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2.45</v>
+      </c>
+      <c r="K98">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L98">
+        <v>1.526</v>
+      </c>
+      <c r="M98">
+        <v>4.73855616</v>
+      </c>
+      <c r="N98">
+        <v>-3.21255616</v>
+      </c>
+      <c r="O98">
+        <v>-0.7710134783999999</v>
+      </c>
+      <c r="P98">
+        <v>-2.4415426816</v>
+      </c>
+      <c r="Q98">
+        <v>-1.5175426816</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.295718202255416</v>
+      </c>
+      <c r="T98">
+        <v>19.78370356138016</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.07728936571261404</v>
+      </c>
+      <c r="W98">
+        <v>0.2203432994678278</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3220390238025586</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2653582955793313</v>
+      </c>
+      <c r="C99">
+        <v>-11.56463315870066</v>
+      </c>
+      <c r="D99">
+        <v>3.705266841299344</v>
+      </c>
+      <c r="E99">
+        <v>10.6799</v>
+      </c>
+      <c r="F99">
+        <v>20.0499</v>
+      </c>
+      <c r="G99">
+        <v>4.78</v>
+      </c>
+      <c r="H99">
+        <v>11.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>2.45</v>
+      </c>
+      <c r="K99">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L99">
+        <v>1.526</v>
+      </c>
+      <c r="M99">
+        <v>4.78791612</v>
+      </c>
+      <c r="N99">
+        <v>-3.26191612</v>
+      </c>
+      <c r="O99">
+        <v>-0.7828598687999999</v>
+      </c>
+      <c r="P99">
+        <v>-2.4790562512</v>
+      </c>
+      <c r="Q99">
+        <v>-1.5550562512</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.714690936340554</v>
+      </c>
+      <c r="T99">
+        <v>26.37827141517355</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.0764925681279479</v>
+      </c>
+      <c r="W99">
+        <v>0.220533574731046</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3187190338664496</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2673582955793313</v>
+      </c>
+      <c r="C100">
+        <v>-11.80375610648217</v>
+      </c>
+      <c r="D100">
+        <v>3.672843893517836</v>
+      </c>
+      <c r="E100">
+        <v>10.8866</v>
+      </c>
+      <c r="F100">
+        <v>20.2566</v>
+      </c>
+      <c r="G100">
+        <v>4.78</v>
+      </c>
+      <c r="H100">
+        <v>11.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2.45</v>
+      </c>
+      <c r="K100">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L100">
+        <v>1.526</v>
+      </c>
+      <c r="M100">
+        <v>4.837276080000001</v>
+      </c>
+      <c r="N100">
+        <v>-3.31127608</v>
+      </c>
+      <c r="O100">
+        <v>-0.7947062592</v>
+      </c>
+      <c r="P100">
+        <v>-2.5165698208</v>
+      </c>
+      <c r="Q100">
+        <v>-1.5925698208</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.552636404510832</v>
+      </c>
+      <c r="T100">
+        <v>39.56740712276032</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.07571203171847905</v>
+      </c>
+      <c r="W100">
+        <v>0.2207199668256272</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.315466798826996</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2693582955793314</v>
+      </c>
+      <c r="C101">
+        <v>-12.0423165423367</v>
+      </c>
+      <c r="D101">
+        <v>3.640983457663303</v>
+      </c>
+      <c r="E101">
+        <v>11.0933</v>
+      </c>
+      <c r="F101">
+        <v>20.4633</v>
+      </c>
+      <c r="G101">
+        <v>4.78</v>
+      </c>
+      <c r="H101">
+        <v>11.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2.45</v>
+      </c>
+      <c r="K101">
+        <v>0.9239999999999999</v>
+      </c>
+      <c r="L101">
+        <v>1.526</v>
+      </c>
+      <c r="M101">
+        <v>4.88663604</v>
+      </c>
+      <c r="N101">
+        <v>-3.36063604</v>
+      </c>
+      <c r="O101">
+        <v>-0.8065526495999999</v>
+      </c>
+      <c r="P101">
+        <v>-2.5540833904</v>
+      </c>
+      <c r="Q101">
+        <v>-1.6300833904</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.066472809021664</v>
+      </c>
+      <c r="T101">
+        <v>79.13481424552064</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.07494726372132271</v>
+      </c>
+      <c r="W101">
+        <v>0.2209025934233482</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3122802655055112</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
